--- a/relationship_data_template.xlsx
+++ b/relationship_data_template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krish\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krish\OneDrive\Desktop\anime_ai\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA981A64-F0F8-4697-B473-A5F0299974E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4723F0A2-C930-42BD-99A3-5D9F2B83CEA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1C80641A-8C68-4CCB-904C-C1A2FE90DEC2}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2124" uniqueCount="335">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4974" uniqueCount="339">
   <si>
     <t>source_name</t>
   </si>
@@ -1036,13 +1036,25 @@
   </si>
   <si>
     <t>char_smoothie_charlotte</t>
+  </si>
+  <si>
+    <t>Konohagakure</t>
+  </si>
+  <si>
+    <t>org_konohagakure</t>
+  </si>
+  <si>
+    <t>member</t>
+  </si>
+  <si>
+    <t>organization</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1195,6 +1207,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF12824D"/>
+      <name val="Courier New"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="33">
@@ -1538,13 +1556,14 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1900,7 +1919,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1F906C6-76EC-4EFB-AFDE-921EF73AD1B4}">
-  <dimension ref="A1:H509"/>
+  <dimension ref="A1:H822"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -8486,6 +8505,650 @@
         <v>94</v>
       </c>
     </row>
+    <row r="365" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A365" t="s">
+        <v>225</v>
+      </c>
+      <c r="B365" t="s">
+        <v>226</v>
+      </c>
+      <c r="C365" t="s">
+        <v>227</v>
+      </c>
+      <c r="D365" t="s">
+        <v>228</v>
+      </c>
+      <c r="E365" t="s">
+        <v>48</v>
+      </c>
+      <c r="F365" t="s">
+        <v>13</v>
+      </c>
+      <c r="H365" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="366" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A366" t="s">
+        <v>225</v>
+      </c>
+      <c r="B366" t="s">
+        <v>226</v>
+      </c>
+      <c r="C366" t="s">
+        <v>229</v>
+      </c>
+      <c r="D366" t="s">
+        <v>334</v>
+      </c>
+      <c r="E366" t="s">
+        <v>48</v>
+      </c>
+      <c r="F366" t="s">
+        <v>13</v>
+      </c>
+      <c r="H366" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="367" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A367" t="s">
+        <v>225</v>
+      </c>
+      <c r="B367" t="s">
+        <v>226</v>
+      </c>
+      <c r="C367" t="s">
+        <v>230</v>
+      </c>
+      <c r="D367" t="s">
+        <v>231</v>
+      </c>
+      <c r="E367" t="s">
+        <v>48</v>
+      </c>
+      <c r="F367" t="s">
+        <v>13</v>
+      </c>
+      <c r="H367" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="368" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A368" t="s">
+        <v>225</v>
+      </c>
+      <c r="B368" t="s">
+        <v>226</v>
+      </c>
+      <c r="C368" t="s">
+        <v>232</v>
+      </c>
+      <c r="D368" t="s">
+        <v>233</v>
+      </c>
+      <c r="E368" t="s">
+        <v>48</v>
+      </c>
+      <c r="F368" t="s">
+        <v>13</v>
+      </c>
+      <c r="H368" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="369" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A369" t="s">
+        <v>225</v>
+      </c>
+      <c r="B369" t="s">
+        <v>226</v>
+      </c>
+      <c r="C369" t="s">
+        <v>234</v>
+      </c>
+      <c r="D369" t="s">
+        <v>235</v>
+      </c>
+      <c r="E369" t="s">
+        <v>48</v>
+      </c>
+      <c r="F369" t="s">
+        <v>13</v>
+      </c>
+      <c r="H369" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="370" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A370" t="s">
+        <v>225</v>
+      </c>
+      <c r="B370" t="s">
+        <v>226</v>
+      </c>
+      <c r="C370" t="s">
+        <v>236</v>
+      </c>
+      <c r="D370" t="s">
+        <v>237</v>
+      </c>
+      <c r="E370" t="s">
+        <v>48</v>
+      </c>
+      <c r="F370" t="s">
+        <v>13</v>
+      </c>
+      <c r="H370" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="371" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A371" t="s">
+        <v>225</v>
+      </c>
+      <c r="B371" t="s">
+        <v>226</v>
+      </c>
+      <c r="C371" t="s">
+        <v>238</v>
+      </c>
+      <c r="D371" t="s">
+        <v>239</v>
+      </c>
+      <c r="E371" t="s">
+        <v>48</v>
+      </c>
+      <c r="F371" t="s">
+        <v>13</v>
+      </c>
+      <c r="H371" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="372" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A372" t="s">
+        <v>225</v>
+      </c>
+      <c r="B372" t="s">
+        <v>226</v>
+      </c>
+      <c r="C372" t="s">
+        <v>240</v>
+      </c>
+      <c r="D372" t="s">
+        <v>241</v>
+      </c>
+      <c r="E372" t="s">
+        <v>48</v>
+      </c>
+      <c r="F372" t="s">
+        <v>13</v>
+      </c>
+      <c r="H372" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="373" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A373" t="s">
+        <v>225</v>
+      </c>
+      <c r="B373" t="s">
+        <v>226</v>
+      </c>
+      <c r="C373" t="s">
+        <v>242</v>
+      </c>
+      <c r="D373" t="s">
+        <v>243</v>
+      </c>
+      <c r="E373" t="s">
+        <v>48</v>
+      </c>
+      <c r="F373" t="s">
+        <v>13</v>
+      </c>
+      <c r="H373" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="374" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A374" t="s">
+        <v>225</v>
+      </c>
+      <c r="B374" t="s">
+        <v>226</v>
+      </c>
+      <c r="C374" t="s">
+        <v>244</v>
+      </c>
+      <c r="D374" t="s">
+        <v>245</v>
+      </c>
+      <c r="E374" t="s">
+        <v>48</v>
+      </c>
+      <c r="F374" t="s">
+        <v>13</v>
+      </c>
+      <c r="H374" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="375" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A375" t="s">
+        <v>225</v>
+      </c>
+      <c r="B375" t="s">
+        <v>226</v>
+      </c>
+      <c r="C375" t="s">
+        <v>246</v>
+      </c>
+      <c r="D375" t="s">
+        <v>247</v>
+      </c>
+      <c r="E375" t="s">
+        <v>48</v>
+      </c>
+      <c r="F375" t="s">
+        <v>13</v>
+      </c>
+      <c r="H375" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="376" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A376" t="s">
+        <v>225</v>
+      </c>
+      <c r="B376" t="s">
+        <v>226</v>
+      </c>
+      <c r="C376" t="s">
+        <v>248</v>
+      </c>
+      <c r="D376" t="s">
+        <v>249</v>
+      </c>
+      <c r="E376" t="s">
+        <v>48</v>
+      </c>
+      <c r="F376" t="s">
+        <v>13</v>
+      </c>
+      <c r="H376" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="377" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A377" t="s">
+        <v>225</v>
+      </c>
+      <c r="B377" t="s">
+        <v>226</v>
+      </c>
+      <c r="C377" t="s">
+        <v>250</v>
+      </c>
+      <c r="D377" t="s">
+        <v>251</v>
+      </c>
+      <c r="E377" t="s">
+        <v>48</v>
+      </c>
+      <c r="F377" t="s">
+        <v>13</v>
+      </c>
+      <c r="H377" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="378" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A378" t="s">
+        <v>225</v>
+      </c>
+      <c r="B378" t="s">
+        <v>226</v>
+      </c>
+      <c r="C378" t="s">
+        <v>252</v>
+      </c>
+      <c r="D378" t="s">
+        <v>253</v>
+      </c>
+      <c r="E378" t="s">
+        <v>48</v>
+      </c>
+      <c r="F378" t="s">
+        <v>13</v>
+      </c>
+      <c r="H378" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="379" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A379" t="s">
+        <v>225</v>
+      </c>
+      <c r="B379" t="s">
+        <v>226</v>
+      </c>
+      <c r="C379" t="s">
+        <v>254</v>
+      </c>
+      <c r="D379" t="s">
+        <v>255</v>
+      </c>
+      <c r="E379" t="s">
+        <v>48</v>
+      </c>
+      <c r="F379" t="s">
+        <v>13</v>
+      </c>
+      <c r="H379" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="380" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A380" t="s">
+        <v>225</v>
+      </c>
+      <c r="B380" t="s">
+        <v>226</v>
+      </c>
+      <c r="C380" t="s">
+        <v>256</v>
+      </c>
+      <c r="D380" t="s">
+        <v>257</v>
+      </c>
+      <c r="E380" t="s">
+        <v>48</v>
+      </c>
+      <c r="F380" t="s">
+        <v>13</v>
+      </c>
+      <c r="H380" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="381" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A381" t="s">
+        <v>225</v>
+      </c>
+      <c r="B381" t="s">
+        <v>226</v>
+      </c>
+      <c r="C381" t="s">
+        <v>258</v>
+      </c>
+      <c r="D381" t="s">
+        <v>259</v>
+      </c>
+      <c r="E381" t="s">
+        <v>48</v>
+      </c>
+      <c r="F381" t="s">
+        <v>13</v>
+      </c>
+      <c r="H381" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="382" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A382" t="s">
+        <v>225</v>
+      </c>
+      <c r="B382" t="s">
+        <v>226</v>
+      </c>
+      <c r="C382" t="s">
+        <v>260</v>
+      </c>
+      <c r="D382" t="s">
+        <v>261</v>
+      </c>
+      <c r="E382" t="s">
+        <v>48</v>
+      </c>
+      <c r="F382" t="s">
+        <v>13</v>
+      </c>
+      <c r="H382" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="383" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A383" t="s">
+        <v>225</v>
+      </c>
+      <c r="B383" t="s">
+        <v>226</v>
+      </c>
+      <c r="C383" t="s">
+        <v>262</v>
+      </c>
+      <c r="D383" t="s">
+        <v>263</v>
+      </c>
+      <c r="E383" t="s">
+        <v>48</v>
+      </c>
+      <c r="F383" t="s">
+        <v>13</v>
+      </c>
+      <c r="H383" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="384" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A384" t="s">
+        <v>225</v>
+      </c>
+      <c r="B384" t="s">
+        <v>226</v>
+      </c>
+      <c r="C384" t="s">
+        <v>264</v>
+      </c>
+      <c r="D384" t="s">
+        <v>265</v>
+      </c>
+      <c r="E384" t="s">
+        <v>48</v>
+      </c>
+      <c r="F384" t="s">
+        <v>13</v>
+      </c>
+      <c r="H384" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="385" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A385" t="s">
+        <v>225</v>
+      </c>
+      <c r="B385" t="s">
+        <v>226</v>
+      </c>
+      <c r="C385" t="s">
+        <v>266</v>
+      </c>
+      <c r="D385" t="s">
+        <v>267</v>
+      </c>
+      <c r="E385" t="s">
+        <v>48</v>
+      </c>
+      <c r="F385" t="s">
+        <v>13</v>
+      </c>
+      <c r="H385" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="386" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A386" t="s">
+        <v>225</v>
+      </c>
+      <c r="B386" t="s">
+        <v>226</v>
+      </c>
+      <c r="C386" t="s">
+        <v>268</v>
+      </c>
+      <c r="D386" t="s">
+        <v>269</v>
+      </c>
+      <c r="E386" t="s">
+        <v>48</v>
+      </c>
+      <c r="F386" t="s">
+        <v>13</v>
+      </c>
+      <c r="H386" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="387" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A387" t="s">
+        <v>225</v>
+      </c>
+      <c r="B387" t="s">
+        <v>226</v>
+      </c>
+      <c r="C387" t="s">
+        <v>270</v>
+      </c>
+      <c r="D387" t="s">
+        <v>271</v>
+      </c>
+      <c r="E387" t="s">
+        <v>48</v>
+      </c>
+      <c r="F387" t="s">
+        <v>13</v>
+      </c>
+      <c r="H387" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="388" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A388" t="s">
+        <v>225</v>
+      </c>
+      <c r="B388" t="s">
+        <v>226</v>
+      </c>
+      <c r="C388" t="s">
+        <v>272</v>
+      </c>
+      <c r="D388" t="s">
+        <v>273</v>
+      </c>
+      <c r="E388" t="s">
+        <v>48</v>
+      </c>
+      <c r="F388" t="s">
+        <v>13</v>
+      </c>
+      <c r="H388" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="389" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A389" t="s">
+        <v>225</v>
+      </c>
+      <c r="B389" t="s">
+        <v>226</v>
+      </c>
+      <c r="C389" t="s">
+        <v>274</v>
+      </c>
+      <c r="D389" t="s">
+        <v>275</v>
+      </c>
+      <c r="E389" t="s">
+        <v>48</v>
+      </c>
+      <c r="F389" t="s">
+        <v>13</v>
+      </c>
+      <c r="H389" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="390" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A390" t="s">
+        <v>225</v>
+      </c>
+      <c r="B390" t="s">
+        <v>226</v>
+      </c>
+      <c r="C390" t="s">
+        <v>276</v>
+      </c>
+      <c r="D390" t="s">
+        <v>277</v>
+      </c>
+      <c r="E390" t="s">
+        <v>48</v>
+      </c>
+      <c r="F390" t="s">
+        <v>13</v>
+      </c>
+      <c r="H390" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="391" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A391" t="s">
+        <v>225</v>
+      </c>
+      <c r="B391" t="s">
+        <v>226</v>
+      </c>
+      <c r="C391" t="s">
+        <v>278</v>
+      </c>
+      <c r="D391" t="s">
+        <v>279</v>
+      </c>
+      <c r="E391" t="s">
+        <v>48</v>
+      </c>
+      <c r="F391" t="s">
+        <v>13</v>
+      </c>
+      <c r="H391" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="392" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A392" t="s">
+        <v>225</v>
+      </c>
+      <c r="B392" t="s">
+        <v>226</v>
+      </c>
+      <c r="C392" t="s">
+        <v>280</v>
+      </c>
+      <c r="D392" t="s">
+        <v>281</v>
+      </c>
+      <c r="E392" t="s">
+        <v>48</v>
+      </c>
+      <c r="F392" t="s">
+        <v>13</v>
+      </c>
+      <c r="H392" t="s">
+        <v>63</v>
+      </c>
+    </row>
     <row r="401" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A401" t="s">
         <v>307</v>
@@ -8716,6 +9379,1800 @@
         <v>78</v>
       </c>
     </row>
+    <row r="421" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A421" t="s">
+        <v>227</v>
+      </c>
+      <c r="B421" t="s">
+        <v>228</v>
+      </c>
+      <c r="C421" t="s">
+        <v>229</v>
+      </c>
+      <c r="D421" t="s">
+        <v>334</v>
+      </c>
+      <c r="E421" t="s">
+        <v>48</v>
+      </c>
+      <c r="F421" t="s">
+        <v>13</v>
+      </c>
+      <c r="H421" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="422" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A422" t="s">
+        <v>227</v>
+      </c>
+      <c r="B422" t="s">
+        <v>228</v>
+      </c>
+      <c r="C422" t="s">
+        <v>230</v>
+      </c>
+      <c r="D422" t="s">
+        <v>231</v>
+      </c>
+      <c r="E422" t="s">
+        <v>48</v>
+      </c>
+      <c r="F422" t="s">
+        <v>13</v>
+      </c>
+      <c r="H422" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="423" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A423" t="s">
+        <v>227</v>
+      </c>
+      <c r="B423" t="s">
+        <v>228</v>
+      </c>
+      <c r="C423" t="s">
+        <v>232</v>
+      </c>
+      <c r="D423" t="s">
+        <v>233</v>
+      </c>
+      <c r="E423" t="s">
+        <v>48</v>
+      </c>
+      <c r="F423" t="s">
+        <v>13</v>
+      </c>
+      <c r="H423" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="424" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A424" t="s">
+        <v>227</v>
+      </c>
+      <c r="B424" t="s">
+        <v>228</v>
+      </c>
+      <c r="C424" t="s">
+        <v>234</v>
+      </c>
+      <c r="D424" t="s">
+        <v>235</v>
+      </c>
+      <c r="E424" t="s">
+        <v>48</v>
+      </c>
+      <c r="F424" t="s">
+        <v>13</v>
+      </c>
+      <c r="H424" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="425" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A425" t="s">
+        <v>227</v>
+      </c>
+      <c r="B425" t="s">
+        <v>228</v>
+      </c>
+      <c r="C425" t="s">
+        <v>236</v>
+      </c>
+      <c r="D425" t="s">
+        <v>237</v>
+      </c>
+      <c r="E425" t="s">
+        <v>48</v>
+      </c>
+      <c r="F425" t="s">
+        <v>13</v>
+      </c>
+      <c r="H425" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="426" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A426" t="s">
+        <v>227</v>
+      </c>
+      <c r="B426" t="s">
+        <v>228</v>
+      </c>
+      <c r="C426" t="s">
+        <v>238</v>
+      </c>
+      <c r="D426" t="s">
+        <v>239</v>
+      </c>
+      <c r="E426" t="s">
+        <v>48</v>
+      </c>
+      <c r="F426" t="s">
+        <v>13</v>
+      </c>
+      <c r="H426" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="427" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A427" t="s">
+        <v>227</v>
+      </c>
+      <c r="B427" t="s">
+        <v>228</v>
+      </c>
+      <c r="C427" t="s">
+        <v>240</v>
+      </c>
+      <c r="D427" t="s">
+        <v>241</v>
+      </c>
+      <c r="E427" t="s">
+        <v>48</v>
+      </c>
+      <c r="F427" t="s">
+        <v>13</v>
+      </c>
+      <c r="H427" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="428" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A428" t="s">
+        <v>227</v>
+      </c>
+      <c r="B428" t="s">
+        <v>228</v>
+      </c>
+      <c r="C428" t="s">
+        <v>242</v>
+      </c>
+      <c r="D428" t="s">
+        <v>243</v>
+      </c>
+      <c r="E428" t="s">
+        <v>48</v>
+      </c>
+      <c r="F428" t="s">
+        <v>13</v>
+      </c>
+      <c r="H428" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="429" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A429" t="s">
+        <v>227</v>
+      </c>
+      <c r="B429" t="s">
+        <v>228</v>
+      </c>
+      <c r="C429" t="s">
+        <v>244</v>
+      </c>
+      <c r="D429" t="s">
+        <v>245</v>
+      </c>
+      <c r="E429" t="s">
+        <v>48</v>
+      </c>
+      <c r="F429" t="s">
+        <v>13</v>
+      </c>
+      <c r="H429" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="430" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A430" t="s">
+        <v>227</v>
+      </c>
+      <c r="B430" t="s">
+        <v>228</v>
+      </c>
+      <c r="C430" t="s">
+        <v>246</v>
+      </c>
+      <c r="D430" t="s">
+        <v>247</v>
+      </c>
+      <c r="E430" t="s">
+        <v>48</v>
+      </c>
+      <c r="F430" t="s">
+        <v>13</v>
+      </c>
+      <c r="H430" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="431" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A431" t="s">
+        <v>227</v>
+      </c>
+      <c r="B431" t="s">
+        <v>228</v>
+      </c>
+      <c r="C431" t="s">
+        <v>248</v>
+      </c>
+      <c r="D431" t="s">
+        <v>249</v>
+      </c>
+      <c r="E431" t="s">
+        <v>48</v>
+      </c>
+      <c r="F431" t="s">
+        <v>13</v>
+      </c>
+      <c r="H431" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="432" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A432" t="s">
+        <v>227</v>
+      </c>
+      <c r="B432" t="s">
+        <v>228</v>
+      </c>
+      <c r="C432" t="s">
+        <v>250</v>
+      </c>
+      <c r="D432" t="s">
+        <v>251</v>
+      </c>
+      <c r="E432" t="s">
+        <v>48</v>
+      </c>
+      <c r="F432" t="s">
+        <v>13</v>
+      </c>
+      <c r="H432" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="433" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A433" t="s">
+        <v>227</v>
+      </c>
+      <c r="B433" t="s">
+        <v>228</v>
+      </c>
+      <c r="C433" t="s">
+        <v>252</v>
+      </c>
+      <c r="D433" t="s">
+        <v>253</v>
+      </c>
+      <c r="E433" t="s">
+        <v>48</v>
+      </c>
+      <c r="F433" t="s">
+        <v>13</v>
+      </c>
+      <c r="H433" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="434" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A434" t="s">
+        <v>227</v>
+      </c>
+      <c r="B434" t="s">
+        <v>228</v>
+      </c>
+      <c r="C434" t="s">
+        <v>254</v>
+      </c>
+      <c r="D434" t="s">
+        <v>255</v>
+      </c>
+      <c r="E434" t="s">
+        <v>48</v>
+      </c>
+      <c r="F434" t="s">
+        <v>13</v>
+      </c>
+      <c r="H434" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="435" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A435" t="s">
+        <v>227</v>
+      </c>
+      <c r="B435" t="s">
+        <v>228</v>
+      </c>
+      <c r="C435" t="s">
+        <v>256</v>
+      </c>
+      <c r="D435" t="s">
+        <v>257</v>
+      </c>
+      <c r="E435" t="s">
+        <v>48</v>
+      </c>
+      <c r="F435" t="s">
+        <v>13</v>
+      </c>
+      <c r="H435" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="436" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A436" t="s">
+        <v>227</v>
+      </c>
+      <c r="B436" t="s">
+        <v>228</v>
+      </c>
+      <c r="C436" t="s">
+        <v>258</v>
+      </c>
+      <c r="D436" t="s">
+        <v>259</v>
+      </c>
+      <c r="E436" t="s">
+        <v>48</v>
+      </c>
+      <c r="F436" t="s">
+        <v>13</v>
+      </c>
+      <c r="H436" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="437" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A437" t="s">
+        <v>227</v>
+      </c>
+      <c r="B437" t="s">
+        <v>228</v>
+      </c>
+      <c r="C437" t="s">
+        <v>260</v>
+      </c>
+      <c r="D437" t="s">
+        <v>261</v>
+      </c>
+      <c r="E437" t="s">
+        <v>48</v>
+      </c>
+      <c r="F437" t="s">
+        <v>13</v>
+      </c>
+      <c r="H437" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="438" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A438" t="s">
+        <v>227</v>
+      </c>
+      <c r="B438" t="s">
+        <v>228</v>
+      </c>
+      <c r="C438" t="s">
+        <v>262</v>
+      </c>
+      <c r="D438" t="s">
+        <v>263</v>
+      </c>
+      <c r="E438" t="s">
+        <v>48</v>
+      </c>
+      <c r="F438" t="s">
+        <v>13</v>
+      </c>
+      <c r="H438" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="439" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A439" t="s">
+        <v>227</v>
+      </c>
+      <c r="B439" t="s">
+        <v>228</v>
+      </c>
+      <c r="C439" t="s">
+        <v>264</v>
+      </c>
+      <c r="D439" t="s">
+        <v>265</v>
+      </c>
+      <c r="E439" t="s">
+        <v>48</v>
+      </c>
+      <c r="F439" t="s">
+        <v>13</v>
+      </c>
+      <c r="H439" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="440" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A440" t="s">
+        <v>227</v>
+      </c>
+      <c r="B440" t="s">
+        <v>228</v>
+      </c>
+      <c r="C440" t="s">
+        <v>266</v>
+      </c>
+      <c r="D440" t="s">
+        <v>267</v>
+      </c>
+      <c r="E440" t="s">
+        <v>48</v>
+      </c>
+      <c r="F440" t="s">
+        <v>13</v>
+      </c>
+      <c r="H440" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="441" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A441" t="s">
+        <v>227</v>
+      </c>
+      <c r="B441" t="s">
+        <v>228</v>
+      </c>
+      <c r="C441" t="s">
+        <v>268</v>
+      </c>
+      <c r="D441" t="s">
+        <v>269</v>
+      </c>
+      <c r="E441" t="s">
+        <v>48</v>
+      </c>
+      <c r="F441" t="s">
+        <v>13</v>
+      </c>
+      <c r="H441" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="442" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A442" t="s">
+        <v>227</v>
+      </c>
+      <c r="B442" t="s">
+        <v>228</v>
+      </c>
+      <c r="C442" t="s">
+        <v>270</v>
+      </c>
+      <c r="D442" t="s">
+        <v>271</v>
+      </c>
+      <c r="E442" t="s">
+        <v>48</v>
+      </c>
+      <c r="F442" t="s">
+        <v>13</v>
+      </c>
+      <c r="H442" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="443" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A443" t="s">
+        <v>227</v>
+      </c>
+      <c r="B443" t="s">
+        <v>228</v>
+      </c>
+      <c r="C443" t="s">
+        <v>272</v>
+      </c>
+      <c r="D443" t="s">
+        <v>273</v>
+      </c>
+      <c r="E443" t="s">
+        <v>48</v>
+      </c>
+      <c r="F443" t="s">
+        <v>13</v>
+      </c>
+      <c r="H443" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="444" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A444" t="s">
+        <v>227</v>
+      </c>
+      <c r="B444" t="s">
+        <v>228</v>
+      </c>
+      <c r="C444" t="s">
+        <v>274</v>
+      </c>
+      <c r="D444" t="s">
+        <v>275</v>
+      </c>
+      <c r="E444" t="s">
+        <v>48</v>
+      </c>
+      <c r="F444" t="s">
+        <v>13</v>
+      </c>
+      <c r="H444" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="445" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A445" t="s">
+        <v>227</v>
+      </c>
+      <c r="B445" t="s">
+        <v>228</v>
+      </c>
+      <c r="C445" t="s">
+        <v>276</v>
+      </c>
+      <c r="D445" t="s">
+        <v>277</v>
+      </c>
+      <c r="E445" t="s">
+        <v>48</v>
+      </c>
+      <c r="F445" t="s">
+        <v>13</v>
+      </c>
+      <c r="H445" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="446" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A446" t="s">
+        <v>227</v>
+      </c>
+      <c r="B446" t="s">
+        <v>228</v>
+      </c>
+      <c r="C446" t="s">
+        <v>278</v>
+      </c>
+      <c r="D446" t="s">
+        <v>279</v>
+      </c>
+      <c r="E446" t="s">
+        <v>48</v>
+      </c>
+      <c r="F446" t="s">
+        <v>13</v>
+      </c>
+      <c r="H446" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="447" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A447" t="s">
+        <v>227</v>
+      </c>
+      <c r="B447" t="s">
+        <v>228</v>
+      </c>
+      <c r="C447" t="s">
+        <v>280</v>
+      </c>
+      <c r="D447" t="s">
+        <v>281</v>
+      </c>
+      <c r="E447" t="s">
+        <v>48</v>
+      </c>
+      <c r="F447" t="s">
+        <v>13</v>
+      </c>
+      <c r="H447" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="448" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A448" t="s">
+        <v>229</v>
+      </c>
+      <c r="B448" t="s">
+        <v>334</v>
+      </c>
+      <c r="C448" t="s">
+        <v>230</v>
+      </c>
+      <c r="D448" t="s">
+        <v>231</v>
+      </c>
+      <c r="E448" t="s">
+        <v>63</v>
+      </c>
+      <c r="F448" t="s">
+        <v>13</v>
+      </c>
+      <c r="H448" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="449" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A449" t="s">
+        <v>229</v>
+      </c>
+      <c r="B449" t="s">
+        <v>334</v>
+      </c>
+      <c r="C449" t="s">
+        <v>232</v>
+      </c>
+      <c r="D449" t="s">
+        <v>233</v>
+      </c>
+      <c r="E449" t="s">
+        <v>63</v>
+      </c>
+      <c r="F449" t="s">
+        <v>13</v>
+      </c>
+      <c r="H449" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="450" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A450" t="s">
+        <v>229</v>
+      </c>
+      <c r="B450" t="s">
+        <v>334</v>
+      </c>
+      <c r="C450" t="s">
+        <v>234</v>
+      </c>
+      <c r="D450" t="s">
+        <v>235</v>
+      </c>
+      <c r="E450" t="s">
+        <v>63</v>
+      </c>
+      <c r="F450" t="s">
+        <v>13</v>
+      </c>
+      <c r="H450" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="451" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A451" t="s">
+        <v>229</v>
+      </c>
+      <c r="B451" t="s">
+        <v>334</v>
+      </c>
+      <c r="C451" t="s">
+        <v>236</v>
+      </c>
+      <c r="D451" t="s">
+        <v>237</v>
+      </c>
+      <c r="E451" t="s">
+        <v>63</v>
+      </c>
+      <c r="F451" t="s">
+        <v>13</v>
+      </c>
+      <c r="H451" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="452" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A452" t="s">
+        <v>229</v>
+      </c>
+      <c r="B452" t="s">
+        <v>334</v>
+      </c>
+      <c r="C452" t="s">
+        <v>238</v>
+      </c>
+      <c r="D452" t="s">
+        <v>239</v>
+      </c>
+      <c r="E452" t="s">
+        <v>63</v>
+      </c>
+      <c r="F452" t="s">
+        <v>13</v>
+      </c>
+      <c r="H452" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="453" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A453" t="s">
+        <v>229</v>
+      </c>
+      <c r="B453" t="s">
+        <v>334</v>
+      </c>
+      <c r="C453" t="s">
+        <v>240</v>
+      </c>
+      <c r="D453" t="s">
+        <v>241</v>
+      </c>
+      <c r="E453" t="s">
+        <v>63</v>
+      </c>
+      <c r="F453" t="s">
+        <v>13</v>
+      </c>
+      <c r="H453" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="454" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A454" t="s">
+        <v>229</v>
+      </c>
+      <c r="B454" t="s">
+        <v>334</v>
+      </c>
+      <c r="C454" t="s">
+        <v>242</v>
+      </c>
+      <c r="D454" t="s">
+        <v>243</v>
+      </c>
+      <c r="E454" t="s">
+        <v>63</v>
+      </c>
+      <c r="F454" t="s">
+        <v>13</v>
+      </c>
+      <c r="H454" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="455" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A455" t="s">
+        <v>229</v>
+      </c>
+      <c r="B455" t="s">
+        <v>334</v>
+      </c>
+      <c r="C455" t="s">
+        <v>244</v>
+      </c>
+      <c r="D455" t="s">
+        <v>245</v>
+      </c>
+      <c r="E455" t="s">
+        <v>63</v>
+      </c>
+      <c r="F455" t="s">
+        <v>13</v>
+      </c>
+      <c r="H455" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="456" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A456" t="s">
+        <v>229</v>
+      </c>
+      <c r="B456" t="s">
+        <v>334</v>
+      </c>
+      <c r="C456" t="s">
+        <v>246</v>
+      </c>
+      <c r="D456" t="s">
+        <v>247</v>
+      </c>
+      <c r="E456" t="s">
+        <v>63</v>
+      </c>
+      <c r="F456" t="s">
+        <v>13</v>
+      </c>
+      <c r="H456" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="457" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A457" t="s">
+        <v>229</v>
+      </c>
+      <c r="B457" t="s">
+        <v>334</v>
+      </c>
+      <c r="C457" t="s">
+        <v>248</v>
+      </c>
+      <c r="D457" t="s">
+        <v>249</v>
+      </c>
+      <c r="E457" t="s">
+        <v>63</v>
+      </c>
+      <c r="F457" t="s">
+        <v>13</v>
+      </c>
+      <c r="H457" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="458" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A458" t="s">
+        <v>229</v>
+      </c>
+      <c r="B458" t="s">
+        <v>334</v>
+      </c>
+      <c r="C458" t="s">
+        <v>250</v>
+      </c>
+      <c r="D458" t="s">
+        <v>251</v>
+      </c>
+      <c r="E458" t="s">
+        <v>63</v>
+      </c>
+      <c r="F458" t="s">
+        <v>13</v>
+      </c>
+      <c r="H458" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="459" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A459" t="s">
+        <v>229</v>
+      </c>
+      <c r="B459" t="s">
+        <v>334</v>
+      </c>
+      <c r="C459" t="s">
+        <v>252</v>
+      </c>
+      <c r="D459" t="s">
+        <v>253</v>
+      </c>
+      <c r="E459" t="s">
+        <v>63</v>
+      </c>
+      <c r="F459" t="s">
+        <v>13</v>
+      </c>
+      <c r="H459" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="460" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A460" t="s">
+        <v>229</v>
+      </c>
+      <c r="B460" t="s">
+        <v>334</v>
+      </c>
+      <c r="C460" t="s">
+        <v>254</v>
+      </c>
+      <c r="D460" t="s">
+        <v>255</v>
+      </c>
+      <c r="E460" t="s">
+        <v>63</v>
+      </c>
+      <c r="F460" t="s">
+        <v>13</v>
+      </c>
+      <c r="H460" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="461" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A461" t="s">
+        <v>229</v>
+      </c>
+      <c r="B461" t="s">
+        <v>334</v>
+      </c>
+      <c r="C461" t="s">
+        <v>256</v>
+      </c>
+      <c r="D461" t="s">
+        <v>257</v>
+      </c>
+      <c r="E461" t="s">
+        <v>63</v>
+      </c>
+      <c r="F461" t="s">
+        <v>13</v>
+      </c>
+      <c r="H461" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="462" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A462" t="s">
+        <v>229</v>
+      </c>
+      <c r="B462" t="s">
+        <v>334</v>
+      </c>
+      <c r="C462" t="s">
+        <v>258</v>
+      </c>
+      <c r="D462" t="s">
+        <v>259</v>
+      </c>
+      <c r="E462" t="s">
+        <v>63</v>
+      </c>
+      <c r="F462" t="s">
+        <v>13</v>
+      </c>
+      <c r="H462" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="463" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A463" t="s">
+        <v>229</v>
+      </c>
+      <c r="B463" t="s">
+        <v>334</v>
+      </c>
+      <c r="C463" t="s">
+        <v>260</v>
+      </c>
+      <c r="D463" t="s">
+        <v>261</v>
+      </c>
+      <c r="E463" t="s">
+        <v>63</v>
+      </c>
+      <c r="F463" t="s">
+        <v>13</v>
+      </c>
+      <c r="H463" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="464" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A464" t="s">
+        <v>229</v>
+      </c>
+      <c r="B464" t="s">
+        <v>334</v>
+      </c>
+      <c r="C464" t="s">
+        <v>262</v>
+      </c>
+      <c r="D464" t="s">
+        <v>263</v>
+      </c>
+      <c r="E464" t="s">
+        <v>63</v>
+      </c>
+      <c r="F464" t="s">
+        <v>13</v>
+      </c>
+      <c r="H464" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="465" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A465" t="s">
+        <v>229</v>
+      </c>
+      <c r="B465" t="s">
+        <v>334</v>
+      </c>
+      <c r="C465" t="s">
+        <v>264</v>
+      </c>
+      <c r="D465" t="s">
+        <v>265</v>
+      </c>
+      <c r="E465" t="s">
+        <v>63</v>
+      </c>
+      <c r="F465" t="s">
+        <v>13</v>
+      </c>
+      <c r="H465" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="466" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A466" t="s">
+        <v>229</v>
+      </c>
+      <c r="B466" t="s">
+        <v>334</v>
+      </c>
+      <c r="C466" t="s">
+        <v>266</v>
+      </c>
+      <c r="D466" t="s">
+        <v>267</v>
+      </c>
+      <c r="E466" t="s">
+        <v>63</v>
+      </c>
+      <c r="F466" t="s">
+        <v>13</v>
+      </c>
+      <c r="H466" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="467" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A467" t="s">
+        <v>229</v>
+      </c>
+      <c r="B467" t="s">
+        <v>334</v>
+      </c>
+      <c r="C467" t="s">
+        <v>268</v>
+      </c>
+      <c r="D467" t="s">
+        <v>269</v>
+      </c>
+      <c r="E467" t="s">
+        <v>63</v>
+      </c>
+      <c r="F467" t="s">
+        <v>13</v>
+      </c>
+      <c r="H467" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="468" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A468" t="s">
+        <v>229</v>
+      </c>
+      <c r="B468" t="s">
+        <v>334</v>
+      </c>
+      <c r="C468" t="s">
+        <v>270</v>
+      </c>
+      <c r="D468" t="s">
+        <v>271</v>
+      </c>
+      <c r="E468" t="s">
+        <v>63</v>
+      </c>
+      <c r="F468" t="s">
+        <v>13</v>
+      </c>
+      <c r="H468" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="469" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A469" t="s">
+        <v>229</v>
+      </c>
+      <c r="B469" t="s">
+        <v>334</v>
+      </c>
+      <c r="C469" t="s">
+        <v>272</v>
+      </c>
+      <c r="D469" t="s">
+        <v>273</v>
+      </c>
+      <c r="E469" t="s">
+        <v>63</v>
+      </c>
+      <c r="F469" t="s">
+        <v>13</v>
+      </c>
+      <c r="H469" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="470" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A470" t="s">
+        <v>229</v>
+      </c>
+      <c r="B470" t="s">
+        <v>334</v>
+      </c>
+      <c r="C470" t="s">
+        <v>274</v>
+      </c>
+      <c r="D470" t="s">
+        <v>275</v>
+      </c>
+      <c r="E470" t="s">
+        <v>63</v>
+      </c>
+      <c r="F470" t="s">
+        <v>13</v>
+      </c>
+      <c r="H470" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="471" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A471" t="s">
+        <v>229</v>
+      </c>
+      <c r="B471" t="s">
+        <v>334</v>
+      </c>
+      <c r="C471" t="s">
+        <v>276</v>
+      </c>
+      <c r="D471" t="s">
+        <v>277</v>
+      </c>
+      <c r="E471" t="s">
+        <v>63</v>
+      </c>
+      <c r="F471" t="s">
+        <v>13</v>
+      </c>
+      <c r="H471" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="472" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A472" t="s">
+        <v>229</v>
+      </c>
+      <c r="B472" t="s">
+        <v>334</v>
+      </c>
+      <c r="C472" t="s">
+        <v>278</v>
+      </c>
+      <c r="D472" t="s">
+        <v>279</v>
+      </c>
+      <c r="E472" t="s">
+        <v>63</v>
+      </c>
+      <c r="F472" t="s">
+        <v>13</v>
+      </c>
+      <c r="H472" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="473" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A473" t="s">
+        <v>229</v>
+      </c>
+      <c r="B473" t="s">
+        <v>334</v>
+      </c>
+      <c r="C473" t="s">
+        <v>280</v>
+      </c>
+      <c r="D473" t="s">
+        <v>281</v>
+      </c>
+      <c r="E473" t="s">
+        <v>63</v>
+      </c>
+      <c r="F473" t="s">
+        <v>13</v>
+      </c>
+      <c r="H473" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="474" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A474" t="s">
+        <v>230</v>
+      </c>
+      <c r="B474" t="s">
+        <v>231</v>
+      </c>
+      <c r="C474" t="s">
+        <v>232</v>
+      </c>
+      <c r="D474" t="s">
+        <v>233</v>
+      </c>
+      <c r="E474" t="s">
+        <v>48</v>
+      </c>
+      <c r="F474" t="s">
+        <v>13</v>
+      </c>
+      <c r="H474" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="475" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A475" t="s">
+        <v>230</v>
+      </c>
+      <c r="B475" t="s">
+        <v>231</v>
+      </c>
+      <c r="C475" t="s">
+        <v>234</v>
+      </c>
+      <c r="D475" t="s">
+        <v>235</v>
+      </c>
+      <c r="E475" t="s">
+        <v>48</v>
+      </c>
+      <c r="F475" t="s">
+        <v>13</v>
+      </c>
+      <c r="H475" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="476" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A476" t="s">
+        <v>230</v>
+      </c>
+      <c r="B476" t="s">
+        <v>231</v>
+      </c>
+      <c r="C476" t="s">
+        <v>236</v>
+      </c>
+      <c r="D476" t="s">
+        <v>237</v>
+      </c>
+      <c r="E476" t="s">
+        <v>48</v>
+      </c>
+      <c r="F476" t="s">
+        <v>13</v>
+      </c>
+      <c r="H476" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="477" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A477" t="s">
+        <v>230</v>
+      </c>
+      <c r="B477" t="s">
+        <v>231</v>
+      </c>
+      <c r="C477" t="s">
+        <v>238</v>
+      </c>
+      <c r="D477" t="s">
+        <v>239</v>
+      </c>
+      <c r="E477" t="s">
+        <v>48</v>
+      </c>
+      <c r="F477" t="s">
+        <v>13</v>
+      </c>
+      <c r="H477" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="478" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A478" t="s">
+        <v>230</v>
+      </c>
+      <c r="B478" t="s">
+        <v>231</v>
+      </c>
+      <c r="C478" t="s">
+        <v>240</v>
+      </c>
+      <c r="D478" t="s">
+        <v>241</v>
+      </c>
+      <c r="E478" t="s">
+        <v>48</v>
+      </c>
+      <c r="F478" t="s">
+        <v>13</v>
+      </c>
+      <c r="H478" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="479" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A479" t="s">
+        <v>230</v>
+      </c>
+      <c r="B479" t="s">
+        <v>231</v>
+      </c>
+      <c r="C479" t="s">
+        <v>242</v>
+      </c>
+      <c r="D479" t="s">
+        <v>243</v>
+      </c>
+      <c r="E479" t="s">
+        <v>48</v>
+      </c>
+      <c r="F479" t="s">
+        <v>13</v>
+      </c>
+      <c r="H479" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="480" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A480" t="s">
+        <v>230</v>
+      </c>
+      <c r="B480" t="s">
+        <v>231</v>
+      </c>
+      <c r="C480" t="s">
+        <v>244</v>
+      </c>
+      <c r="D480" t="s">
+        <v>245</v>
+      </c>
+      <c r="E480" t="s">
+        <v>48</v>
+      </c>
+      <c r="F480" t="s">
+        <v>13</v>
+      </c>
+      <c r="H480" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="481" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A481" t="s">
+        <v>230</v>
+      </c>
+      <c r="B481" t="s">
+        <v>231</v>
+      </c>
+      <c r="C481" t="s">
+        <v>246</v>
+      </c>
+      <c r="D481" t="s">
+        <v>247</v>
+      </c>
+      <c r="E481" t="s">
+        <v>48</v>
+      </c>
+      <c r="F481" t="s">
+        <v>13</v>
+      </c>
+      <c r="H481" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="482" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A482" t="s">
+        <v>230</v>
+      </c>
+      <c r="B482" t="s">
+        <v>231</v>
+      </c>
+      <c r="C482" t="s">
+        <v>248</v>
+      </c>
+      <c r="D482" t="s">
+        <v>249</v>
+      </c>
+      <c r="E482" t="s">
+        <v>48</v>
+      </c>
+      <c r="F482" t="s">
+        <v>13</v>
+      </c>
+      <c r="H482" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="483" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A483" t="s">
+        <v>230</v>
+      </c>
+      <c r="B483" t="s">
+        <v>231</v>
+      </c>
+      <c r="C483" t="s">
+        <v>250</v>
+      </c>
+      <c r="D483" t="s">
+        <v>251</v>
+      </c>
+      <c r="E483" t="s">
+        <v>48</v>
+      </c>
+      <c r="F483" t="s">
+        <v>13</v>
+      </c>
+      <c r="H483" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="484" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A484" t="s">
+        <v>230</v>
+      </c>
+      <c r="B484" t="s">
+        <v>231</v>
+      </c>
+      <c r="C484" t="s">
+        <v>252</v>
+      </c>
+      <c r="D484" t="s">
+        <v>253</v>
+      </c>
+      <c r="E484" t="s">
+        <v>48</v>
+      </c>
+      <c r="F484" t="s">
+        <v>13</v>
+      </c>
+      <c r="H484" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="485" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A485" t="s">
+        <v>230</v>
+      </c>
+      <c r="B485" t="s">
+        <v>231</v>
+      </c>
+      <c r="C485" t="s">
+        <v>254</v>
+      </c>
+      <c r="D485" t="s">
+        <v>255</v>
+      </c>
+      <c r="E485" t="s">
+        <v>48</v>
+      </c>
+      <c r="F485" t="s">
+        <v>13</v>
+      </c>
+      <c r="H485" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="486" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A486" t="s">
+        <v>230</v>
+      </c>
+      <c r="B486" t="s">
+        <v>231</v>
+      </c>
+      <c r="C486" t="s">
+        <v>256</v>
+      </c>
+      <c r="D486" t="s">
+        <v>257</v>
+      </c>
+      <c r="E486" t="s">
+        <v>48</v>
+      </c>
+      <c r="F486" t="s">
+        <v>13</v>
+      </c>
+      <c r="H486" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="487" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A487" t="s">
+        <v>230</v>
+      </c>
+      <c r="B487" t="s">
+        <v>231</v>
+      </c>
+      <c r="C487" t="s">
+        <v>258</v>
+      </c>
+      <c r="D487" t="s">
+        <v>259</v>
+      </c>
+      <c r="E487" t="s">
+        <v>48</v>
+      </c>
+      <c r="F487" t="s">
+        <v>13</v>
+      </c>
+      <c r="H487" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="488" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A488" t="s">
+        <v>230</v>
+      </c>
+      <c r="B488" t="s">
+        <v>231</v>
+      </c>
+      <c r="C488" t="s">
+        <v>260</v>
+      </c>
+      <c r="D488" t="s">
+        <v>261</v>
+      </c>
+      <c r="E488" t="s">
+        <v>48</v>
+      </c>
+      <c r="F488" t="s">
+        <v>13</v>
+      </c>
+      <c r="H488" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="489" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A489" t="s">
+        <v>230</v>
+      </c>
+      <c r="B489" t="s">
+        <v>231</v>
+      </c>
+      <c r="C489" t="s">
+        <v>262</v>
+      </c>
+      <c r="D489" t="s">
+        <v>263</v>
+      </c>
+      <c r="E489" t="s">
+        <v>48</v>
+      </c>
+      <c r="F489" t="s">
+        <v>13</v>
+      </c>
+      <c r="H489" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="490" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A490" t="s">
+        <v>230</v>
+      </c>
+      <c r="B490" t="s">
+        <v>231</v>
+      </c>
+      <c r="C490" t="s">
+        <v>264</v>
+      </c>
+      <c r="D490" t="s">
+        <v>265</v>
+      </c>
+      <c r="E490" t="s">
+        <v>48</v>
+      </c>
+      <c r="F490" t="s">
+        <v>13</v>
+      </c>
+      <c r="H490" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="491" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A491" t="s">
+        <v>230</v>
+      </c>
+      <c r="B491" t="s">
+        <v>231</v>
+      </c>
+      <c r="C491" t="s">
+        <v>266</v>
+      </c>
+      <c r="D491" t="s">
+        <v>267</v>
+      </c>
+      <c r="E491" t="s">
+        <v>48</v>
+      </c>
+      <c r="F491" t="s">
+        <v>13</v>
+      </c>
+      <c r="H491" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="492" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A492" t="s">
+        <v>230</v>
+      </c>
+      <c r="B492" t="s">
+        <v>231</v>
+      </c>
+      <c r="C492" t="s">
+        <v>268</v>
+      </c>
+      <c r="D492" t="s">
+        <v>269</v>
+      </c>
+      <c r="E492" t="s">
+        <v>48</v>
+      </c>
+      <c r="F492" t="s">
+        <v>13</v>
+      </c>
+      <c r="H492" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="493" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A493" t="s">
+        <v>230</v>
+      </c>
+      <c r="B493" t="s">
+        <v>231</v>
+      </c>
+      <c r="C493" t="s">
+        <v>270</v>
+      </c>
+      <c r="D493" t="s">
+        <v>271</v>
+      </c>
+      <c r="E493" t="s">
+        <v>48</v>
+      </c>
+      <c r="F493" t="s">
+        <v>13</v>
+      </c>
+      <c r="H493" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="494" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A494" t="s">
+        <v>230</v>
+      </c>
+      <c r="B494" t="s">
+        <v>231</v>
+      </c>
+      <c r="C494" t="s">
+        <v>272</v>
+      </c>
+      <c r="D494" t="s">
+        <v>273</v>
+      </c>
+      <c r="E494" t="s">
+        <v>48</v>
+      </c>
+      <c r="F494" t="s">
+        <v>13</v>
+      </c>
+      <c r="H494" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="495" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A495" t="s">
+        <v>230</v>
+      </c>
+      <c r="B495" t="s">
+        <v>231</v>
+      </c>
+      <c r="C495" t="s">
+        <v>274</v>
+      </c>
+      <c r="D495" t="s">
+        <v>275</v>
+      </c>
+      <c r="E495" t="s">
+        <v>48</v>
+      </c>
+      <c r="F495" t="s">
+        <v>13</v>
+      </c>
+      <c r="H495" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="496" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A496" t="s">
+        <v>230</v>
+      </c>
+      <c r="B496" t="s">
+        <v>231</v>
+      </c>
+      <c r="C496" t="s">
+        <v>276</v>
+      </c>
+      <c r="D496" t="s">
+        <v>277</v>
+      </c>
+      <c r="E496" t="s">
+        <v>48</v>
+      </c>
+      <c r="F496" t="s">
+        <v>13</v>
+      </c>
+      <c r="H496" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="497" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A497" t="s">
+        <v>230</v>
+      </c>
+      <c r="B497" t="s">
+        <v>231</v>
+      </c>
+      <c r="C497" t="s">
+        <v>278</v>
+      </c>
+      <c r="D497" t="s">
+        <v>279</v>
+      </c>
+      <c r="E497" t="s">
+        <v>48</v>
+      </c>
+      <c r="F497" t="s">
+        <v>13</v>
+      </c>
+      <c r="H497" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="498" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A498" t="s">
+        <v>230</v>
+      </c>
+      <c r="B498" t="s">
+        <v>231</v>
+      </c>
+      <c r="C498" t="s">
+        <v>280</v>
+      </c>
+      <c r="D498" t="s">
+        <v>281</v>
+      </c>
+      <c r="E498" t="s">
+        <v>48</v>
+      </c>
+      <c r="F498" t="s">
+        <v>13</v>
+      </c>
+      <c r="H498" t="s">
+        <v>63</v>
+      </c>
+    </row>
     <row r="501" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A501" t="s">
         <v>317</v>
@@ -8921,6 +11378,6934 @@
       </c>
       <c r="H509" t="s">
         <v>94</v>
+      </c>
+    </row>
+    <row r="511" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A511" t="s">
+        <v>232</v>
+      </c>
+      <c r="B511" t="s">
+        <v>233</v>
+      </c>
+      <c r="C511" t="s">
+        <v>234</v>
+      </c>
+      <c r="D511" t="s">
+        <v>235</v>
+      </c>
+      <c r="E511" t="s">
+        <v>48</v>
+      </c>
+      <c r="F511" t="s">
+        <v>13</v>
+      </c>
+      <c r="H511" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="512" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A512" t="s">
+        <v>232</v>
+      </c>
+      <c r="B512" t="s">
+        <v>233</v>
+      </c>
+      <c r="C512" t="s">
+        <v>236</v>
+      </c>
+      <c r="D512" t="s">
+        <v>237</v>
+      </c>
+      <c r="E512" t="s">
+        <v>48</v>
+      </c>
+      <c r="F512" t="s">
+        <v>13</v>
+      </c>
+      <c r="H512" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="513" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A513" t="s">
+        <v>232</v>
+      </c>
+      <c r="B513" t="s">
+        <v>233</v>
+      </c>
+      <c r="C513" t="s">
+        <v>238</v>
+      </c>
+      <c r="D513" t="s">
+        <v>239</v>
+      </c>
+      <c r="E513" t="s">
+        <v>48</v>
+      </c>
+      <c r="F513" t="s">
+        <v>13</v>
+      </c>
+      <c r="H513" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="514" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A514" t="s">
+        <v>232</v>
+      </c>
+      <c r="B514" t="s">
+        <v>233</v>
+      </c>
+      <c r="C514" t="s">
+        <v>240</v>
+      </c>
+      <c r="D514" t="s">
+        <v>241</v>
+      </c>
+      <c r="E514" t="s">
+        <v>48</v>
+      </c>
+      <c r="F514" t="s">
+        <v>13</v>
+      </c>
+      <c r="H514" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="515" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A515" t="s">
+        <v>232</v>
+      </c>
+      <c r="B515" t="s">
+        <v>233</v>
+      </c>
+      <c r="C515" t="s">
+        <v>242</v>
+      </c>
+      <c r="D515" t="s">
+        <v>243</v>
+      </c>
+      <c r="E515" t="s">
+        <v>48</v>
+      </c>
+      <c r="F515" t="s">
+        <v>13</v>
+      </c>
+      <c r="H515" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="516" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A516" t="s">
+        <v>232</v>
+      </c>
+      <c r="B516" t="s">
+        <v>233</v>
+      </c>
+      <c r="C516" t="s">
+        <v>244</v>
+      </c>
+      <c r="D516" t="s">
+        <v>245</v>
+      </c>
+      <c r="E516" t="s">
+        <v>48</v>
+      </c>
+      <c r="F516" t="s">
+        <v>13</v>
+      </c>
+      <c r="H516" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="517" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A517" t="s">
+        <v>232</v>
+      </c>
+      <c r="B517" t="s">
+        <v>233</v>
+      </c>
+      <c r="C517" t="s">
+        <v>246</v>
+      </c>
+      <c r="D517" t="s">
+        <v>247</v>
+      </c>
+      <c r="E517" t="s">
+        <v>48</v>
+      </c>
+      <c r="F517" t="s">
+        <v>13</v>
+      </c>
+      <c r="H517" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="518" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A518" t="s">
+        <v>232</v>
+      </c>
+      <c r="B518" t="s">
+        <v>233</v>
+      </c>
+      <c r="C518" t="s">
+        <v>248</v>
+      </c>
+      <c r="D518" t="s">
+        <v>249</v>
+      </c>
+      <c r="E518" t="s">
+        <v>48</v>
+      </c>
+      <c r="F518" t="s">
+        <v>13</v>
+      </c>
+      <c r="H518" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="519" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A519" t="s">
+        <v>232</v>
+      </c>
+      <c r="B519" t="s">
+        <v>233</v>
+      </c>
+      <c r="C519" t="s">
+        <v>250</v>
+      </c>
+      <c r="D519" t="s">
+        <v>251</v>
+      </c>
+      <c r="E519" t="s">
+        <v>48</v>
+      </c>
+      <c r="F519" t="s">
+        <v>13</v>
+      </c>
+      <c r="H519" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="520" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A520" t="s">
+        <v>232</v>
+      </c>
+      <c r="B520" t="s">
+        <v>233</v>
+      </c>
+      <c r="C520" t="s">
+        <v>252</v>
+      </c>
+      <c r="D520" t="s">
+        <v>253</v>
+      </c>
+      <c r="E520" t="s">
+        <v>48</v>
+      </c>
+      <c r="F520" t="s">
+        <v>13</v>
+      </c>
+      <c r="H520" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="521" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A521" t="s">
+        <v>232</v>
+      </c>
+      <c r="B521" t="s">
+        <v>233</v>
+      </c>
+      <c r="C521" t="s">
+        <v>254</v>
+      </c>
+      <c r="D521" t="s">
+        <v>255</v>
+      </c>
+      <c r="E521" t="s">
+        <v>48</v>
+      </c>
+      <c r="F521" t="s">
+        <v>13</v>
+      </c>
+      <c r="H521" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="522" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A522" t="s">
+        <v>232</v>
+      </c>
+      <c r="B522" t="s">
+        <v>233</v>
+      </c>
+      <c r="C522" t="s">
+        <v>256</v>
+      </c>
+      <c r="D522" t="s">
+        <v>257</v>
+      </c>
+      <c r="E522" t="s">
+        <v>48</v>
+      </c>
+      <c r="F522" t="s">
+        <v>13</v>
+      </c>
+      <c r="H522" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="523" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A523" t="s">
+        <v>232</v>
+      </c>
+      <c r="B523" t="s">
+        <v>233</v>
+      </c>
+      <c r="C523" t="s">
+        <v>258</v>
+      </c>
+      <c r="D523" t="s">
+        <v>259</v>
+      </c>
+      <c r="E523" t="s">
+        <v>48</v>
+      </c>
+      <c r="F523" t="s">
+        <v>13</v>
+      </c>
+      <c r="H523" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="524" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A524" t="s">
+        <v>232</v>
+      </c>
+      <c r="B524" t="s">
+        <v>233</v>
+      </c>
+      <c r="C524" t="s">
+        <v>260</v>
+      </c>
+      <c r="D524" t="s">
+        <v>261</v>
+      </c>
+      <c r="E524" t="s">
+        <v>48</v>
+      </c>
+      <c r="F524" t="s">
+        <v>13</v>
+      </c>
+      <c r="H524" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="525" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A525" t="s">
+        <v>232</v>
+      </c>
+      <c r="B525" t="s">
+        <v>233</v>
+      </c>
+      <c r="C525" t="s">
+        <v>262</v>
+      </c>
+      <c r="D525" t="s">
+        <v>263</v>
+      </c>
+      <c r="E525" t="s">
+        <v>48</v>
+      </c>
+      <c r="F525" t="s">
+        <v>13</v>
+      </c>
+      <c r="H525" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="526" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A526" t="s">
+        <v>232</v>
+      </c>
+      <c r="B526" t="s">
+        <v>233</v>
+      </c>
+      <c r="C526" t="s">
+        <v>264</v>
+      </c>
+      <c r="D526" t="s">
+        <v>265</v>
+      </c>
+      <c r="E526" t="s">
+        <v>48</v>
+      </c>
+      <c r="F526" t="s">
+        <v>13</v>
+      </c>
+      <c r="H526" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="527" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A527" t="s">
+        <v>232</v>
+      </c>
+      <c r="B527" t="s">
+        <v>233</v>
+      </c>
+      <c r="C527" t="s">
+        <v>266</v>
+      </c>
+      <c r="D527" t="s">
+        <v>267</v>
+      </c>
+      <c r="E527" t="s">
+        <v>48</v>
+      </c>
+      <c r="F527" t="s">
+        <v>13</v>
+      </c>
+      <c r="H527" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="528" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A528" t="s">
+        <v>232</v>
+      </c>
+      <c r="B528" t="s">
+        <v>233</v>
+      </c>
+      <c r="C528" t="s">
+        <v>268</v>
+      </c>
+      <c r="D528" t="s">
+        <v>269</v>
+      </c>
+      <c r="E528" t="s">
+        <v>48</v>
+      </c>
+      <c r="F528" t="s">
+        <v>13</v>
+      </c>
+      <c r="H528" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="529" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A529" t="s">
+        <v>232</v>
+      </c>
+      <c r="B529" t="s">
+        <v>233</v>
+      </c>
+      <c r="C529" t="s">
+        <v>270</v>
+      </c>
+      <c r="D529" t="s">
+        <v>271</v>
+      </c>
+      <c r="E529" t="s">
+        <v>48</v>
+      </c>
+      <c r="F529" t="s">
+        <v>13</v>
+      </c>
+      <c r="H529" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="530" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A530" t="s">
+        <v>232</v>
+      </c>
+      <c r="B530" t="s">
+        <v>233</v>
+      </c>
+      <c r="C530" t="s">
+        <v>272</v>
+      </c>
+      <c r="D530" t="s">
+        <v>273</v>
+      </c>
+      <c r="E530" t="s">
+        <v>48</v>
+      </c>
+      <c r="F530" t="s">
+        <v>13</v>
+      </c>
+      <c r="H530" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="531" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A531" t="s">
+        <v>232</v>
+      </c>
+      <c r="B531" t="s">
+        <v>233</v>
+      </c>
+      <c r="C531" t="s">
+        <v>274</v>
+      </c>
+      <c r="D531" t="s">
+        <v>275</v>
+      </c>
+      <c r="E531" t="s">
+        <v>48</v>
+      </c>
+      <c r="F531" t="s">
+        <v>13</v>
+      </c>
+      <c r="H531" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="532" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A532" t="s">
+        <v>232</v>
+      </c>
+      <c r="B532" t="s">
+        <v>233</v>
+      </c>
+      <c r="C532" t="s">
+        <v>276</v>
+      </c>
+      <c r="D532" t="s">
+        <v>277</v>
+      </c>
+      <c r="E532" t="s">
+        <v>48</v>
+      </c>
+      <c r="F532" t="s">
+        <v>13</v>
+      </c>
+      <c r="H532" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="533" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A533" t="s">
+        <v>232</v>
+      </c>
+      <c r="B533" t="s">
+        <v>233</v>
+      </c>
+      <c r="C533" t="s">
+        <v>278</v>
+      </c>
+      <c r="D533" t="s">
+        <v>279</v>
+      </c>
+      <c r="E533" t="s">
+        <v>48</v>
+      </c>
+      <c r="F533" t="s">
+        <v>13</v>
+      </c>
+      <c r="H533" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="534" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A534" t="s">
+        <v>232</v>
+      </c>
+      <c r="B534" t="s">
+        <v>233</v>
+      </c>
+      <c r="C534" t="s">
+        <v>280</v>
+      </c>
+      <c r="D534" t="s">
+        <v>281</v>
+      </c>
+      <c r="E534" t="s">
+        <v>48</v>
+      </c>
+      <c r="F534" t="s">
+        <v>13</v>
+      </c>
+      <c r="H534" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="535" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A535" t="s">
+        <v>234</v>
+      </c>
+      <c r="B535" t="s">
+        <v>235</v>
+      </c>
+      <c r="C535" t="s">
+        <v>236</v>
+      </c>
+      <c r="D535" t="s">
+        <v>237</v>
+      </c>
+      <c r="E535" t="s">
+        <v>63</v>
+      </c>
+      <c r="F535" t="s">
+        <v>13</v>
+      </c>
+      <c r="H535" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="536" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A536" t="s">
+        <v>234</v>
+      </c>
+      <c r="B536" t="s">
+        <v>235</v>
+      </c>
+      <c r="C536" t="s">
+        <v>238</v>
+      </c>
+      <c r="D536" t="s">
+        <v>239</v>
+      </c>
+      <c r="E536" t="s">
+        <v>63</v>
+      </c>
+      <c r="F536" t="s">
+        <v>13</v>
+      </c>
+      <c r="H536" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="537" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A537" t="s">
+        <v>234</v>
+      </c>
+      <c r="B537" t="s">
+        <v>235</v>
+      </c>
+      <c r="C537" t="s">
+        <v>240</v>
+      </c>
+      <c r="D537" t="s">
+        <v>241</v>
+      </c>
+      <c r="E537" t="s">
+        <v>63</v>
+      </c>
+      <c r="F537" t="s">
+        <v>13</v>
+      </c>
+      <c r="H537" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="538" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A538" t="s">
+        <v>234</v>
+      </c>
+      <c r="B538" t="s">
+        <v>235</v>
+      </c>
+      <c r="C538" t="s">
+        <v>242</v>
+      </c>
+      <c r="D538" t="s">
+        <v>243</v>
+      </c>
+      <c r="E538" t="s">
+        <v>63</v>
+      </c>
+      <c r="F538" t="s">
+        <v>13</v>
+      </c>
+      <c r="H538" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="539" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A539" t="s">
+        <v>234</v>
+      </c>
+      <c r="B539" t="s">
+        <v>235</v>
+      </c>
+      <c r="C539" t="s">
+        <v>244</v>
+      </c>
+      <c r="D539" t="s">
+        <v>245</v>
+      </c>
+      <c r="E539" t="s">
+        <v>63</v>
+      </c>
+      <c r="F539" t="s">
+        <v>13</v>
+      </c>
+      <c r="H539" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="540" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A540" t="s">
+        <v>234</v>
+      </c>
+      <c r="B540" t="s">
+        <v>235</v>
+      </c>
+      <c r="C540" t="s">
+        <v>246</v>
+      </c>
+      <c r="D540" t="s">
+        <v>247</v>
+      </c>
+      <c r="E540" t="s">
+        <v>63</v>
+      </c>
+      <c r="F540" t="s">
+        <v>13</v>
+      </c>
+      <c r="H540" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="541" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A541" t="s">
+        <v>234</v>
+      </c>
+      <c r="B541" t="s">
+        <v>235</v>
+      </c>
+      <c r="C541" t="s">
+        <v>248</v>
+      </c>
+      <c r="D541" t="s">
+        <v>249</v>
+      </c>
+      <c r="E541" t="s">
+        <v>63</v>
+      </c>
+      <c r="F541" t="s">
+        <v>13</v>
+      </c>
+      <c r="H541" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="542" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A542" t="s">
+        <v>234</v>
+      </c>
+      <c r="B542" t="s">
+        <v>235</v>
+      </c>
+      <c r="C542" t="s">
+        <v>250</v>
+      </c>
+      <c r="D542" t="s">
+        <v>251</v>
+      </c>
+      <c r="E542" t="s">
+        <v>63</v>
+      </c>
+      <c r="F542" t="s">
+        <v>13</v>
+      </c>
+      <c r="H542" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="543" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A543" t="s">
+        <v>234</v>
+      </c>
+      <c r="B543" t="s">
+        <v>235</v>
+      </c>
+      <c r="C543" t="s">
+        <v>252</v>
+      </c>
+      <c r="D543" t="s">
+        <v>253</v>
+      </c>
+      <c r="E543" t="s">
+        <v>63</v>
+      </c>
+      <c r="F543" t="s">
+        <v>13</v>
+      </c>
+      <c r="H543" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="544" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A544" t="s">
+        <v>234</v>
+      </c>
+      <c r="B544" t="s">
+        <v>235</v>
+      </c>
+      <c r="C544" t="s">
+        <v>254</v>
+      </c>
+      <c r="D544" t="s">
+        <v>255</v>
+      </c>
+      <c r="E544" t="s">
+        <v>63</v>
+      </c>
+      <c r="F544" t="s">
+        <v>13</v>
+      </c>
+      <c r="H544" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="545" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A545" t="s">
+        <v>234</v>
+      </c>
+      <c r="B545" t="s">
+        <v>235</v>
+      </c>
+      <c r="C545" t="s">
+        <v>256</v>
+      </c>
+      <c r="D545" t="s">
+        <v>257</v>
+      </c>
+      <c r="E545" t="s">
+        <v>63</v>
+      </c>
+      <c r="F545" t="s">
+        <v>13</v>
+      </c>
+      <c r="H545" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="546" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A546" t="s">
+        <v>234</v>
+      </c>
+      <c r="B546" t="s">
+        <v>235</v>
+      </c>
+      <c r="C546" t="s">
+        <v>258</v>
+      </c>
+      <c r="D546" t="s">
+        <v>259</v>
+      </c>
+      <c r="E546" t="s">
+        <v>63</v>
+      </c>
+      <c r="F546" t="s">
+        <v>13</v>
+      </c>
+      <c r="H546" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="547" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A547" t="s">
+        <v>234</v>
+      </c>
+      <c r="B547" t="s">
+        <v>235</v>
+      </c>
+      <c r="C547" t="s">
+        <v>260</v>
+      </c>
+      <c r="D547" t="s">
+        <v>261</v>
+      </c>
+      <c r="E547" t="s">
+        <v>63</v>
+      </c>
+      <c r="F547" t="s">
+        <v>13</v>
+      </c>
+      <c r="H547" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="548" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A548" t="s">
+        <v>234</v>
+      </c>
+      <c r="B548" t="s">
+        <v>235</v>
+      </c>
+      <c r="C548" t="s">
+        <v>262</v>
+      </c>
+      <c r="D548" t="s">
+        <v>263</v>
+      </c>
+      <c r="E548" t="s">
+        <v>63</v>
+      </c>
+      <c r="F548" t="s">
+        <v>13</v>
+      </c>
+      <c r="H548" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="549" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A549" t="s">
+        <v>234</v>
+      </c>
+      <c r="B549" t="s">
+        <v>235</v>
+      </c>
+      <c r="C549" t="s">
+        <v>264</v>
+      </c>
+      <c r="D549" t="s">
+        <v>265</v>
+      </c>
+      <c r="E549" t="s">
+        <v>63</v>
+      </c>
+      <c r="F549" t="s">
+        <v>13</v>
+      </c>
+      <c r="H549" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="550" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A550" t="s">
+        <v>234</v>
+      </c>
+      <c r="B550" t="s">
+        <v>235</v>
+      </c>
+      <c r="C550" t="s">
+        <v>266</v>
+      </c>
+      <c r="D550" t="s">
+        <v>267</v>
+      </c>
+      <c r="E550" t="s">
+        <v>63</v>
+      </c>
+      <c r="F550" t="s">
+        <v>13</v>
+      </c>
+      <c r="H550" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="551" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A551" t="s">
+        <v>234</v>
+      </c>
+      <c r="B551" t="s">
+        <v>235</v>
+      </c>
+      <c r="C551" t="s">
+        <v>268</v>
+      </c>
+      <c r="D551" t="s">
+        <v>269</v>
+      </c>
+      <c r="E551" t="s">
+        <v>63</v>
+      </c>
+      <c r="F551" t="s">
+        <v>13</v>
+      </c>
+      <c r="H551" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="552" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A552" t="s">
+        <v>234</v>
+      </c>
+      <c r="B552" t="s">
+        <v>235</v>
+      </c>
+      <c r="C552" t="s">
+        <v>270</v>
+      </c>
+      <c r="D552" t="s">
+        <v>271</v>
+      </c>
+      <c r="E552" t="s">
+        <v>63</v>
+      </c>
+      <c r="F552" t="s">
+        <v>13</v>
+      </c>
+      <c r="H552" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="553" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A553" t="s">
+        <v>234</v>
+      </c>
+      <c r="B553" t="s">
+        <v>235</v>
+      </c>
+      <c r="C553" t="s">
+        <v>272</v>
+      </c>
+      <c r="D553" t="s">
+        <v>273</v>
+      </c>
+      <c r="E553" t="s">
+        <v>63</v>
+      </c>
+      <c r="F553" t="s">
+        <v>13</v>
+      </c>
+      <c r="H553" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="554" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A554" t="s">
+        <v>234</v>
+      </c>
+      <c r="B554" t="s">
+        <v>235</v>
+      </c>
+      <c r="C554" t="s">
+        <v>274</v>
+      </c>
+      <c r="D554" t="s">
+        <v>275</v>
+      </c>
+      <c r="E554" t="s">
+        <v>63</v>
+      </c>
+      <c r="F554" t="s">
+        <v>13</v>
+      </c>
+      <c r="H554" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="555" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A555" t="s">
+        <v>234</v>
+      </c>
+      <c r="B555" t="s">
+        <v>235</v>
+      </c>
+      <c r="C555" t="s">
+        <v>276</v>
+      </c>
+      <c r="D555" t="s">
+        <v>277</v>
+      </c>
+      <c r="E555" t="s">
+        <v>63</v>
+      </c>
+      <c r="F555" t="s">
+        <v>13</v>
+      </c>
+      <c r="H555" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="556" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A556" t="s">
+        <v>234</v>
+      </c>
+      <c r="B556" t="s">
+        <v>235</v>
+      </c>
+      <c r="C556" t="s">
+        <v>278</v>
+      </c>
+      <c r="D556" t="s">
+        <v>279</v>
+      </c>
+      <c r="E556" t="s">
+        <v>63</v>
+      </c>
+      <c r="F556" t="s">
+        <v>13</v>
+      </c>
+      <c r="H556" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="557" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A557" t="s">
+        <v>234</v>
+      </c>
+      <c r="B557" t="s">
+        <v>235</v>
+      </c>
+      <c r="C557" t="s">
+        <v>280</v>
+      </c>
+      <c r="D557" t="s">
+        <v>281</v>
+      </c>
+      <c r="E557" t="s">
+        <v>63</v>
+      </c>
+      <c r="F557" t="s">
+        <v>13</v>
+      </c>
+      <c r="H557" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="558" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A558" t="s">
+        <v>236</v>
+      </c>
+      <c r="B558" t="s">
+        <v>237</v>
+      </c>
+      <c r="C558" t="s">
+        <v>238</v>
+      </c>
+      <c r="D558" t="s">
+        <v>239</v>
+      </c>
+      <c r="E558" t="s">
+        <v>63</v>
+      </c>
+      <c r="F558" t="s">
+        <v>13</v>
+      </c>
+      <c r="H558" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="559" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A559" t="s">
+        <v>236</v>
+      </c>
+      <c r="B559" t="s">
+        <v>237</v>
+      </c>
+      <c r="C559" t="s">
+        <v>240</v>
+      </c>
+      <c r="D559" t="s">
+        <v>241</v>
+      </c>
+      <c r="E559" t="s">
+        <v>63</v>
+      </c>
+      <c r="F559" t="s">
+        <v>13</v>
+      </c>
+      <c r="H559" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="560" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A560" t="s">
+        <v>236</v>
+      </c>
+      <c r="B560" t="s">
+        <v>237</v>
+      </c>
+      <c r="C560" t="s">
+        <v>242</v>
+      </c>
+      <c r="D560" t="s">
+        <v>243</v>
+      </c>
+      <c r="E560" t="s">
+        <v>63</v>
+      </c>
+      <c r="F560" t="s">
+        <v>13</v>
+      </c>
+      <c r="H560" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="561" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A561" t="s">
+        <v>236</v>
+      </c>
+      <c r="B561" t="s">
+        <v>237</v>
+      </c>
+      <c r="C561" t="s">
+        <v>244</v>
+      </c>
+      <c r="D561" t="s">
+        <v>245</v>
+      </c>
+      <c r="E561" t="s">
+        <v>63</v>
+      </c>
+      <c r="F561" t="s">
+        <v>13</v>
+      </c>
+      <c r="H561" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="562" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A562" t="s">
+        <v>236</v>
+      </c>
+      <c r="B562" t="s">
+        <v>237</v>
+      </c>
+      <c r="C562" t="s">
+        <v>246</v>
+      </c>
+      <c r="D562" t="s">
+        <v>247</v>
+      </c>
+      <c r="E562" t="s">
+        <v>63</v>
+      </c>
+      <c r="F562" t="s">
+        <v>13</v>
+      </c>
+      <c r="H562" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="563" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A563" t="s">
+        <v>236</v>
+      </c>
+      <c r="B563" t="s">
+        <v>237</v>
+      </c>
+      <c r="C563" t="s">
+        <v>248</v>
+      </c>
+      <c r="D563" t="s">
+        <v>249</v>
+      </c>
+      <c r="E563" t="s">
+        <v>63</v>
+      </c>
+      <c r="F563" t="s">
+        <v>13</v>
+      </c>
+      <c r="H563" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="564" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A564" t="s">
+        <v>236</v>
+      </c>
+      <c r="B564" t="s">
+        <v>237</v>
+      </c>
+      <c r="C564" t="s">
+        <v>250</v>
+      </c>
+      <c r="D564" t="s">
+        <v>251</v>
+      </c>
+      <c r="E564" t="s">
+        <v>63</v>
+      </c>
+      <c r="F564" t="s">
+        <v>13</v>
+      </c>
+      <c r="H564" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="565" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A565" t="s">
+        <v>236</v>
+      </c>
+      <c r="B565" t="s">
+        <v>237</v>
+      </c>
+      <c r="C565" t="s">
+        <v>252</v>
+      </c>
+      <c r="D565" t="s">
+        <v>253</v>
+      </c>
+      <c r="E565" t="s">
+        <v>63</v>
+      </c>
+      <c r="F565" t="s">
+        <v>13</v>
+      </c>
+      <c r="H565" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="566" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A566" t="s">
+        <v>236</v>
+      </c>
+      <c r="B566" t="s">
+        <v>237</v>
+      </c>
+      <c r="C566" t="s">
+        <v>254</v>
+      </c>
+      <c r="D566" t="s">
+        <v>255</v>
+      </c>
+      <c r="E566" t="s">
+        <v>63</v>
+      </c>
+      <c r="F566" t="s">
+        <v>13</v>
+      </c>
+      <c r="H566" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="567" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A567" t="s">
+        <v>236</v>
+      </c>
+      <c r="B567" t="s">
+        <v>237</v>
+      </c>
+      <c r="C567" t="s">
+        <v>256</v>
+      </c>
+      <c r="D567" t="s">
+        <v>257</v>
+      </c>
+      <c r="E567" t="s">
+        <v>63</v>
+      </c>
+      <c r="F567" t="s">
+        <v>13</v>
+      </c>
+      <c r="H567" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="568" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A568" t="s">
+        <v>236</v>
+      </c>
+      <c r="B568" t="s">
+        <v>237</v>
+      </c>
+      <c r="C568" t="s">
+        <v>258</v>
+      </c>
+      <c r="D568" t="s">
+        <v>259</v>
+      </c>
+      <c r="E568" t="s">
+        <v>63</v>
+      </c>
+      <c r="F568" t="s">
+        <v>13</v>
+      </c>
+      <c r="H568" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="569" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A569" t="s">
+        <v>236</v>
+      </c>
+      <c r="B569" t="s">
+        <v>237</v>
+      </c>
+      <c r="C569" t="s">
+        <v>260</v>
+      </c>
+      <c r="D569" t="s">
+        <v>261</v>
+      </c>
+      <c r="E569" t="s">
+        <v>63</v>
+      </c>
+      <c r="F569" t="s">
+        <v>13</v>
+      </c>
+      <c r="H569" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="570" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A570" t="s">
+        <v>236</v>
+      </c>
+      <c r="B570" t="s">
+        <v>237</v>
+      </c>
+      <c r="C570" t="s">
+        <v>262</v>
+      </c>
+      <c r="D570" t="s">
+        <v>263</v>
+      </c>
+      <c r="E570" t="s">
+        <v>63</v>
+      </c>
+      <c r="F570" t="s">
+        <v>13</v>
+      </c>
+      <c r="H570" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="571" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A571" t="s">
+        <v>236</v>
+      </c>
+      <c r="B571" t="s">
+        <v>237</v>
+      </c>
+      <c r="C571" t="s">
+        <v>264</v>
+      </c>
+      <c r="D571" t="s">
+        <v>265</v>
+      </c>
+      <c r="E571" t="s">
+        <v>63</v>
+      </c>
+      <c r="F571" t="s">
+        <v>13</v>
+      </c>
+      <c r="H571" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="572" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A572" t="s">
+        <v>236</v>
+      </c>
+      <c r="B572" t="s">
+        <v>237</v>
+      </c>
+      <c r="C572" t="s">
+        <v>266</v>
+      </c>
+      <c r="D572" t="s">
+        <v>267</v>
+      </c>
+      <c r="E572" t="s">
+        <v>63</v>
+      </c>
+      <c r="F572" t="s">
+        <v>13</v>
+      </c>
+      <c r="H572" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="573" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A573" t="s">
+        <v>236</v>
+      </c>
+      <c r="B573" t="s">
+        <v>237</v>
+      </c>
+      <c r="C573" t="s">
+        <v>268</v>
+      </c>
+      <c r="D573" t="s">
+        <v>269</v>
+      </c>
+      <c r="E573" t="s">
+        <v>63</v>
+      </c>
+      <c r="F573" t="s">
+        <v>13</v>
+      </c>
+      <c r="H573" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="574" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A574" t="s">
+        <v>236</v>
+      </c>
+      <c r="B574" t="s">
+        <v>237</v>
+      </c>
+      <c r="C574" t="s">
+        <v>270</v>
+      </c>
+      <c r="D574" t="s">
+        <v>271</v>
+      </c>
+      <c r="E574" t="s">
+        <v>63</v>
+      </c>
+      <c r="F574" t="s">
+        <v>13</v>
+      </c>
+      <c r="H574" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="575" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A575" t="s">
+        <v>236</v>
+      </c>
+      <c r="B575" t="s">
+        <v>237</v>
+      </c>
+      <c r="C575" t="s">
+        <v>272</v>
+      </c>
+      <c r="D575" t="s">
+        <v>273</v>
+      </c>
+      <c r="E575" t="s">
+        <v>63</v>
+      </c>
+      <c r="F575" t="s">
+        <v>13</v>
+      </c>
+      <c r="H575" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="576" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A576" t="s">
+        <v>236</v>
+      </c>
+      <c r="B576" t="s">
+        <v>237</v>
+      </c>
+      <c r="C576" t="s">
+        <v>274</v>
+      </c>
+      <c r="D576" t="s">
+        <v>275</v>
+      </c>
+      <c r="E576" t="s">
+        <v>63</v>
+      </c>
+      <c r="F576" t="s">
+        <v>13</v>
+      </c>
+      <c r="H576" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="577" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A577" t="s">
+        <v>236</v>
+      </c>
+      <c r="B577" t="s">
+        <v>237</v>
+      </c>
+      <c r="C577" t="s">
+        <v>276</v>
+      </c>
+      <c r="D577" t="s">
+        <v>277</v>
+      </c>
+      <c r="E577" t="s">
+        <v>63</v>
+      </c>
+      <c r="F577" t="s">
+        <v>13</v>
+      </c>
+      <c r="H577" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="578" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A578" t="s">
+        <v>236</v>
+      </c>
+      <c r="B578" t="s">
+        <v>237</v>
+      </c>
+      <c r="C578" t="s">
+        <v>278</v>
+      </c>
+      <c r="D578" t="s">
+        <v>279</v>
+      </c>
+      <c r="E578" t="s">
+        <v>63</v>
+      </c>
+      <c r="F578" t="s">
+        <v>13</v>
+      </c>
+      <c r="H578" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="579" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A579" t="s">
+        <v>236</v>
+      </c>
+      <c r="B579" t="s">
+        <v>237</v>
+      </c>
+      <c r="C579" t="s">
+        <v>280</v>
+      </c>
+      <c r="D579" t="s">
+        <v>281</v>
+      </c>
+      <c r="E579" t="s">
+        <v>63</v>
+      </c>
+      <c r="F579" t="s">
+        <v>13</v>
+      </c>
+      <c r="H579" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="580" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A580" t="s">
+        <v>238</v>
+      </c>
+      <c r="B580" t="s">
+        <v>239</v>
+      </c>
+      <c r="C580" t="s">
+        <v>240</v>
+      </c>
+      <c r="D580" t="s">
+        <v>241</v>
+      </c>
+      <c r="E580" t="s">
+        <v>63</v>
+      </c>
+      <c r="F580" t="s">
+        <v>13</v>
+      </c>
+      <c r="H580" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="581" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A581" t="s">
+        <v>238</v>
+      </c>
+      <c r="B581" t="s">
+        <v>239</v>
+      </c>
+      <c r="C581" t="s">
+        <v>242</v>
+      </c>
+      <c r="D581" t="s">
+        <v>243</v>
+      </c>
+      <c r="E581" t="s">
+        <v>63</v>
+      </c>
+      <c r="F581" t="s">
+        <v>13</v>
+      </c>
+      <c r="H581" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="582" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A582" t="s">
+        <v>238</v>
+      </c>
+      <c r="B582" t="s">
+        <v>239</v>
+      </c>
+      <c r="C582" t="s">
+        <v>244</v>
+      </c>
+      <c r="D582" t="s">
+        <v>245</v>
+      </c>
+      <c r="E582" t="s">
+        <v>63</v>
+      </c>
+      <c r="F582" t="s">
+        <v>13</v>
+      </c>
+      <c r="H582" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="583" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A583" t="s">
+        <v>238</v>
+      </c>
+      <c r="B583" t="s">
+        <v>239</v>
+      </c>
+      <c r="C583" t="s">
+        <v>246</v>
+      </c>
+      <c r="D583" t="s">
+        <v>247</v>
+      </c>
+      <c r="E583" t="s">
+        <v>63</v>
+      </c>
+      <c r="F583" t="s">
+        <v>13</v>
+      </c>
+      <c r="H583" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="584" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A584" t="s">
+        <v>238</v>
+      </c>
+      <c r="B584" t="s">
+        <v>239</v>
+      </c>
+      <c r="C584" t="s">
+        <v>248</v>
+      </c>
+      <c r="D584" t="s">
+        <v>249</v>
+      </c>
+      <c r="E584" t="s">
+        <v>63</v>
+      </c>
+      <c r="F584" t="s">
+        <v>13</v>
+      </c>
+      <c r="H584" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="585" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A585" t="s">
+        <v>238</v>
+      </c>
+      <c r="B585" t="s">
+        <v>239</v>
+      </c>
+      <c r="C585" t="s">
+        <v>250</v>
+      </c>
+      <c r="D585" t="s">
+        <v>251</v>
+      </c>
+      <c r="E585" t="s">
+        <v>63</v>
+      </c>
+      <c r="F585" t="s">
+        <v>13</v>
+      </c>
+      <c r="H585" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="586" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A586" t="s">
+        <v>238</v>
+      </c>
+      <c r="B586" t="s">
+        <v>239</v>
+      </c>
+      <c r="C586" t="s">
+        <v>252</v>
+      </c>
+      <c r="D586" t="s">
+        <v>253</v>
+      </c>
+      <c r="E586" t="s">
+        <v>63</v>
+      </c>
+      <c r="F586" t="s">
+        <v>13</v>
+      </c>
+      <c r="H586" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="587" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A587" t="s">
+        <v>238</v>
+      </c>
+      <c r="B587" t="s">
+        <v>239</v>
+      </c>
+      <c r="C587" t="s">
+        <v>254</v>
+      </c>
+      <c r="D587" t="s">
+        <v>255</v>
+      </c>
+      <c r="E587" t="s">
+        <v>63</v>
+      </c>
+      <c r="F587" t="s">
+        <v>13</v>
+      </c>
+      <c r="H587" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="588" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A588" t="s">
+        <v>238</v>
+      </c>
+      <c r="B588" t="s">
+        <v>239</v>
+      </c>
+      <c r="C588" t="s">
+        <v>256</v>
+      </c>
+      <c r="D588" t="s">
+        <v>257</v>
+      </c>
+      <c r="E588" t="s">
+        <v>63</v>
+      </c>
+      <c r="F588" t="s">
+        <v>13</v>
+      </c>
+      <c r="H588" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="589" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A589" t="s">
+        <v>238</v>
+      </c>
+      <c r="B589" t="s">
+        <v>239</v>
+      </c>
+      <c r="C589" t="s">
+        <v>258</v>
+      </c>
+      <c r="D589" t="s">
+        <v>259</v>
+      </c>
+      <c r="E589" t="s">
+        <v>63</v>
+      </c>
+      <c r="F589" t="s">
+        <v>13</v>
+      </c>
+      <c r="H589" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="590" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A590" t="s">
+        <v>238</v>
+      </c>
+      <c r="B590" t="s">
+        <v>239</v>
+      </c>
+      <c r="C590" t="s">
+        <v>260</v>
+      </c>
+      <c r="D590" t="s">
+        <v>261</v>
+      </c>
+      <c r="E590" t="s">
+        <v>63</v>
+      </c>
+      <c r="F590" t="s">
+        <v>13</v>
+      </c>
+      <c r="H590" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="591" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A591" t="s">
+        <v>238</v>
+      </c>
+      <c r="B591" t="s">
+        <v>239</v>
+      </c>
+      <c r="C591" t="s">
+        <v>262</v>
+      </c>
+      <c r="D591" t="s">
+        <v>263</v>
+      </c>
+      <c r="E591" t="s">
+        <v>63</v>
+      </c>
+      <c r="F591" t="s">
+        <v>13</v>
+      </c>
+      <c r="H591" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="592" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A592" t="s">
+        <v>238</v>
+      </c>
+      <c r="B592" t="s">
+        <v>239</v>
+      </c>
+      <c r="C592" t="s">
+        <v>264</v>
+      </c>
+      <c r="D592" t="s">
+        <v>265</v>
+      </c>
+      <c r="E592" t="s">
+        <v>63</v>
+      </c>
+      <c r="F592" t="s">
+        <v>13</v>
+      </c>
+      <c r="H592" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="593" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A593" t="s">
+        <v>238</v>
+      </c>
+      <c r="B593" t="s">
+        <v>239</v>
+      </c>
+      <c r="C593" t="s">
+        <v>266</v>
+      </c>
+      <c r="D593" t="s">
+        <v>267</v>
+      </c>
+      <c r="E593" t="s">
+        <v>63</v>
+      </c>
+      <c r="F593" t="s">
+        <v>13</v>
+      </c>
+      <c r="H593" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="594" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A594" t="s">
+        <v>238</v>
+      </c>
+      <c r="B594" t="s">
+        <v>239</v>
+      </c>
+      <c r="C594" t="s">
+        <v>268</v>
+      </c>
+      <c r="D594" t="s">
+        <v>269</v>
+      </c>
+      <c r="E594" t="s">
+        <v>63</v>
+      </c>
+      <c r="F594" t="s">
+        <v>13</v>
+      </c>
+      <c r="H594" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="595" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A595" t="s">
+        <v>238</v>
+      </c>
+      <c r="B595" t="s">
+        <v>239</v>
+      </c>
+      <c r="C595" t="s">
+        <v>270</v>
+      </c>
+      <c r="D595" t="s">
+        <v>271</v>
+      </c>
+      <c r="E595" t="s">
+        <v>63</v>
+      </c>
+      <c r="F595" t="s">
+        <v>13</v>
+      </c>
+      <c r="H595" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="596" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A596" t="s">
+        <v>238</v>
+      </c>
+      <c r="B596" t="s">
+        <v>239</v>
+      </c>
+      <c r="C596" t="s">
+        <v>272</v>
+      </c>
+      <c r="D596" t="s">
+        <v>273</v>
+      </c>
+      <c r="E596" t="s">
+        <v>63</v>
+      </c>
+      <c r="F596" t="s">
+        <v>13</v>
+      </c>
+      <c r="H596" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="597" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A597" t="s">
+        <v>238</v>
+      </c>
+      <c r="B597" t="s">
+        <v>239</v>
+      </c>
+      <c r="C597" t="s">
+        <v>274</v>
+      </c>
+      <c r="D597" t="s">
+        <v>275</v>
+      </c>
+      <c r="E597" t="s">
+        <v>63</v>
+      </c>
+      <c r="F597" t="s">
+        <v>13</v>
+      </c>
+      <c r="H597" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="598" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A598" t="s">
+        <v>238</v>
+      </c>
+      <c r="B598" t="s">
+        <v>239</v>
+      </c>
+      <c r="C598" t="s">
+        <v>276</v>
+      </c>
+      <c r="D598" t="s">
+        <v>277</v>
+      </c>
+      <c r="E598" t="s">
+        <v>63</v>
+      </c>
+      <c r="F598" t="s">
+        <v>13</v>
+      </c>
+      <c r="H598" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="599" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A599" t="s">
+        <v>238</v>
+      </c>
+      <c r="B599" t="s">
+        <v>239</v>
+      </c>
+      <c r="C599" t="s">
+        <v>278</v>
+      </c>
+      <c r="D599" t="s">
+        <v>279</v>
+      </c>
+      <c r="E599" t="s">
+        <v>63</v>
+      </c>
+      <c r="F599" t="s">
+        <v>13</v>
+      </c>
+      <c r="H599" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="600" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A600" t="s">
+        <v>238</v>
+      </c>
+      <c r="B600" t="s">
+        <v>239</v>
+      </c>
+      <c r="C600" t="s">
+        <v>280</v>
+      </c>
+      <c r="D600" t="s">
+        <v>281</v>
+      </c>
+      <c r="E600" t="s">
+        <v>63</v>
+      </c>
+      <c r="F600" t="s">
+        <v>13</v>
+      </c>
+      <c r="H600" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="601" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A601" t="s">
+        <v>240</v>
+      </c>
+      <c r="B601" t="s">
+        <v>241</v>
+      </c>
+      <c r="C601" t="s">
+        <v>242</v>
+      </c>
+      <c r="D601" t="s">
+        <v>243</v>
+      </c>
+      <c r="E601" t="s">
+        <v>48</v>
+      </c>
+      <c r="F601" t="s">
+        <v>13</v>
+      </c>
+      <c r="H601" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="602" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A602" t="s">
+        <v>240</v>
+      </c>
+      <c r="B602" t="s">
+        <v>241</v>
+      </c>
+      <c r="C602" t="s">
+        <v>244</v>
+      </c>
+      <c r="D602" t="s">
+        <v>245</v>
+      </c>
+      <c r="E602" t="s">
+        <v>48</v>
+      </c>
+      <c r="F602" t="s">
+        <v>13</v>
+      </c>
+      <c r="H602" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="603" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A603" t="s">
+        <v>240</v>
+      </c>
+      <c r="B603" t="s">
+        <v>241</v>
+      </c>
+      <c r="C603" t="s">
+        <v>246</v>
+      </c>
+      <c r="D603" t="s">
+        <v>247</v>
+      </c>
+      <c r="E603" t="s">
+        <v>48</v>
+      </c>
+      <c r="F603" t="s">
+        <v>13</v>
+      </c>
+      <c r="H603" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="604" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A604" t="s">
+        <v>240</v>
+      </c>
+      <c r="B604" t="s">
+        <v>241</v>
+      </c>
+      <c r="C604" t="s">
+        <v>248</v>
+      </c>
+      <c r="D604" t="s">
+        <v>249</v>
+      </c>
+      <c r="E604" t="s">
+        <v>48</v>
+      </c>
+      <c r="F604" t="s">
+        <v>13</v>
+      </c>
+      <c r="H604" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="605" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A605" t="s">
+        <v>240</v>
+      </c>
+      <c r="B605" t="s">
+        <v>241</v>
+      </c>
+      <c r="C605" t="s">
+        <v>250</v>
+      </c>
+      <c r="D605" t="s">
+        <v>251</v>
+      </c>
+      <c r="E605" t="s">
+        <v>48</v>
+      </c>
+      <c r="F605" t="s">
+        <v>13</v>
+      </c>
+      <c r="H605" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="606" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A606" t="s">
+        <v>240</v>
+      </c>
+      <c r="B606" t="s">
+        <v>241</v>
+      </c>
+      <c r="C606" t="s">
+        <v>252</v>
+      </c>
+      <c r="D606" t="s">
+        <v>253</v>
+      </c>
+      <c r="E606" t="s">
+        <v>48</v>
+      </c>
+      <c r="F606" t="s">
+        <v>13</v>
+      </c>
+      <c r="H606" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="607" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A607" t="s">
+        <v>240</v>
+      </c>
+      <c r="B607" t="s">
+        <v>241</v>
+      </c>
+      <c r="C607" t="s">
+        <v>254</v>
+      </c>
+      <c r="D607" t="s">
+        <v>255</v>
+      </c>
+      <c r="E607" t="s">
+        <v>48</v>
+      </c>
+      <c r="F607" t="s">
+        <v>13</v>
+      </c>
+      <c r="H607" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="608" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A608" t="s">
+        <v>240</v>
+      </c>
+      <c r="B608" t="s">
+        <v>241</v>
+      </c>
+      <c r="C608" t="s">
+        <v>256</v>
+      </c>
+      <c r="D608" t="s">
+        <v>257</v>
+      </c>
+      <c r="E608" t="s">
+        <v>48</v>
+      </c>
+      <c r="F608" t="s">
+        <v>13</v>
+      </c>
+      <c r="H608" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="609" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A609" t="s">
+        <v>240</v>
+      </c>
+      <c r="B609" t="s">
+        <v>241</v>
+      </c>
+      <c r="C609" t="s">
+        <v>258</v>
+      </c>
+      <c r="D609" t="s">
+        <v>259</v>
+      </c>
+      <c r="E609" t="s">
+        <v>48</v>
+      </c>
+      <c r="F609" t="s">
+        <v>13</v>
+      </c>
+      <c r="H609" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="610" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A610" t="s">
+        <v>240</v>
+      </c>
+      <c r="B610" t="s">
+        <v>241</v>
+      </c>
+      <c r="C610" t="s">
+        <v>260</v>
+      </c>
+      <c r="D610" t="s">
+        <v>261</v>
+      </c>
+      <c r="E610" t="s">
+        <v>48</v>
+      </c>
+      <c r="F610" t="s">
+        <v>13</v>
+      </c>
+      <c r="H610" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="611" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A611" t="s">
+        <v>240</v>
+      </c>
+      <c r="B611" t="s">
+        <v>241</v>
+      </c>
+      <c r="C611" t="s">
+        <v>262</v>
+      </c>
+      <c r="D611" t="s">
+        <v>263</v>
+      </c>
+      <c r="E611" t="s">
+        <v>48</v>
+      </c>
+      <c r="F611" t="s">
+        <v>13</v>
+      </c>
+      <c r="H611" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="612" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A612" t="s">
+        <v>240</v>
+      </c>
+      <c r="B612" t="s">
+        <v>241</v>
+      </c>
+      <c r="C612" t="s">
+        <v>264</v>
+      </c>
+      <c r="D612" t="s">
+        <v>265</v>
+      </c>
+      <c r="E612" t="s">
+        <v>48</v>
+      </c>
+      <c r="F612" t="s">
+        <v>13</v>
+      </c>
+      <c r="H612" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="613" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A613" t="s">
+        <v>240</v>
+      </c>
+      <c r="B613" t="s">
+        <v>241</v>
+      </c>
+      <c r="C613" t="s">
+        <v>266</v>
+      </c>
+      <c r="D613" t="s">
+        <v>267</v>
+      </c>
+      <c r="E613" t="s">
+        <v>48</v>
+      </c>
+      <c r="F613" t="s">
+        <v>13</v>
+      </c>
+      <c r="H613" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="614" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A614" t="s">
+        <v>240</v>
+      </c>
+      <c r="B614" t="s">
+        <v>241</v>
+      </c>
+      <c r="C614" t="s">
+        <v>268</v>
+      </c>
+      <c r="D614" t="s">
+        <v>269</v>
+      </c>
+      <c r="E614" t="s">
+        <v>48</v>
+      </c>
+      <c r="F614" t="s">
+        <v>13</v>
+      </c>
+      <c r="H614" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="615" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A615" t="s">
+        <v>240</v>
+      </c>
+      <c r="B615" t="s">
+        <v>241</v>
+      </c>
+      <c r="C615" t="s">
+        <v>270</v>
+      </c>
+      <c r="D615" t="s">
+        <v>271</v>
+      </c>
+      <c r="E615" t="s">
+        <v>48</v>
+      </c>
+      <c r="F615" t="s">
+        <v>13</v>
+      </c>
+      <c r="H615" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="616" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A616" t="s">
+        <v>240</v>
+      </c>
+      <c r="B616" t="s">
+        <v>241</v>
+      </c>
+      <c r="C616" t="s">
+        <v>272</v>
+      </c>
+      <c r="D616" t="s">
+        <v>273</v>
+      </c>
+      <c r="E616" t="s">
+        <v>48</v>
+      </c>
+      <c r="F616" t="s">
+        <v>13</v>
+      </c>
+      <c r="H616" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="617" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A617" t="s">
+        <v>240</v>
+      </c>
+      <c r="B617" t="s">
+        <v>241</v>
+      </c>
+      <c r="C617" t="s">
+        <v>274</v>
+      </c>
+      <c r="D617" t="s">
+        <v>275</v>
+      </c>
+      <c r="E617" t="s">
+        <v>48</v>
+      </c>
+      <c r="F617" t="s">
+        <v>13</v>
+      </c>
+      <c r="H617" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="618" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A618" t="s">
+        <v>240</v>
+      </c>
+      <c r="B618" t="s">
+        <v>241</v>
+      </c>
+      <c r="C618" t="s">
+        <v>276</v>
+      </c>
+      <c r="D618" t="s">
+        <v>277</v>
+      </c>
+      <c r="E618" t="s">
+        <v>48</v>
+      </c>
+      <c r="F618" t="s">
+        <v>13</v>
+      </c>
+      <c r="H618" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="619" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A619" t="s">
+        <v>240</v>
+      </c>
+      <c r="B619" t="s">
+        <v>241</v>
+      </c>
+      <c r="C619" t="s">
+        <v>278</v>
+      </c>
+      <c r="D619" t="s">
+        <v>279</v>
+      </c>
+      <c r="E619" t="s">
+        <v>48</v>
+      </c>
+      <c r="F619" t="s">
+        <v>13</v>
+      </c>
+      <c r="H619" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="620" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A620" t="s">
+        <v>240</v>
+      </c>
+      <c r="B620" t="s">
+        <v>241</v>
+      </c>
+      <c r="C620" t="s">
+        <v>280</v>
+      </c>
+      <c r="D620" t="s">
+        <v>281</v>
+      </c>
+      <c r="E620" t="s">
+        <v>48</v>
+      </c>
+      <c r="F620" t="s">
+        <v>13</v>
+      </c>
+      <c r="H620" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="621" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A621" t="s">
+        <v>242</v>
+      </c>
+      <c r="B621" t="s">
+        <v>243</v>
+      </c>
+      <c r="C621" t="s">
+        <v>244</v>
+      </c>
+      <c r="D621" t="s">
+        <v>245</v>
+      </c>
+      <c r="E621" t="s">
+        <v>48</v>
+      </c>
+      <c r="F621" t="s">
+        <v>13</v>
+      </c>
+      <c r="H621" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="622" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A622" t="s">
+        <v>242</v>
+      </c>
+      <c r="B622" t="s">
+        <v>243</v>
+      </c>
+      <c r="C622" t="s">
+        <v>246</v>
+      </c>
+      <c r="D622" t="s">
+        <v>247</v>
+      </c>
+      <c r="E622" t="s">
+        <v>48</v>
+      </c>
+      <c r="F622" t="s">
+        <v>13</v>
+      </c>
+      <c r="H622" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="623" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A623" t="s">
+        <v>242</v>
+      </c>
+      <c r="B623" t="s">
+        <v>243</v>
+      </c>
+      <c r="C623" t="s">
+        <v>248</v>
+      </c>
+      <c r="D623" t="s">
+        <v>249</v>
+      </c>
+      <c r="E623" t="s">
+        <v>48</v>
+      </c>
+      <c r="F623" t="s">
+        <v>13</v>
+      </c>
+      <c r="H623" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="624" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A624" t="s">
+        <v>242</v>
+      </c>
+      <c r="B624" t="s">
+        <v>243</v>
+      </c>
+      <c r="C624" t="s">
+        <v>250</v>
+      </c>
+      <c r="D624" t="s">
+        <v>251</v>
+      </c>
+      <c r="E624" t="s">
+        <v>48</v>
+      </c>
+      <c r="F624" t="s">
+        <v>13</v>
+      </c>
+      <c r="H624" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="625" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A625" t="s">
+        <v>242</v>
+      </c>
+      <c r="B625" t="s">
+        <v>243</v>
+      </c>
+      <c r="C625" t="s">
+        <v>252</v>
+      </c>
+      <c r="D625" t="s">
+        <v>253</v>
+      </c>
+      <c r="E625" t="s">
+        <v>48</v>
+      </c>
+      <c r="F625" t="s">
+        <v>13</v>
+      </c>
+      <c r="H625" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="626" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A626" t="s">
+        <v>242</v>
+      </c>
+      <c r="B626" t="s">
+        <v>243</v>
+      </c>
+      <c r="C626" t="s">
+        <v>254</v>
+      </c>
+      <c r="D626" t="s">
+        <v>255</v>
+      </c>
+      <c r="E626" t="s">
+        <v>48</v>
+      </c>
+      <c r="F626" t="s">
+        <v>13</v>
+      </c>
+      <c r="H626" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="627" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A627" t="s">
+        <v>242</v>
+      </c>
+      <c r="B627" t="s">
+        <v>243</v>
+      </c>
+      <c r="C627" t="s">
+        <v>256</v>
+      </c>
+      <c r="D627" t="s">
+        <v>257</v>
+      </c>
+      <c r="E627" t="s">
+        <v>48</v>
+      </c>
+      <c r="F627" t="s">
+        <v>13</v>
+      </c>
+      <c r="H627" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="628" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A628" t="s">
+        <v>242</v>
+      </c>
+      <c r="B628" t="s">
+        <v>243</v>
+      </c>
+      <c r="C628" t="s">
+        <v>258</v>
+      </c>
+      <c r="D628" t="s">
+        <v>259</v>
+      </c>
+      <c r="E628" t="s">
+        <v>48</v>
+      </c>
+      <c r="F628" t="s">
+        <v>13</v>
+      </c>
+      <c r="H628" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="629" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A629" t="s">
+        <v>242</v>
+      </c>
+      <c r="B629" t="s">
+        <v>243</v>
+      </c>
+      <c r="C629" t="s">
+        <v>260</v>
+      </c>
+      <c r="D629" t="s">
+        <v>261</v>
+      </c>
+      <c r="E629" t="s">
+        <v>48</v>
+      </c>
+      <c r="F629" t="s">
+        <v>13</v>
+      </c>
+      <c r="H629" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="630" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A630" t="s">
+        <v>242</v>
+      </c>
+      <c r="B630" t="s">
+        <v>243</v>
+      </c>
+      <c r="C630" t="s">
+        <v>262</v>
+      </c>
+      <c r="D630" t="s">
+        <v>263</v>
+      </c>
+      <c r="E630" t="s">
+        <v>48</v>
+      </c>
+      <c r="F630" t="s">
+        <v>13</v>
+      </c>
+      <c r="H630" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="631" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A631" t="s">
+        <v>242</v>
+      </c>
+      <c r="B631" t="s">
+        <v>243</v>
+      </c>
+      <c r="C631" t="s">
+        <v>264</v>
+      </c>
+      <c r="D631" t="s">
+        <v>265</v>
+      </c>
+      <c r="E631" t="s">
+        <v>48</v>
+      </c>
+      <c r="F631" t="s">
+        <v>13</v>
+      </c>
+      <c r="H631" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="632" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A632" t="s">
+        <v>242</v>
+      </c>
+      <c r="B632" t="s">
+        <v>243</v>
+      </c>
+      <c r="C632" t="s">
+        <v>266</v>
+      </c>
+      <c r="D632" t="s">
+        <v>267</v>
+      </c>
+      <c r="E632" t="s">
+        <v>48</v>
+      </c>
+      <c r="F632" t="s">
+        <v>13</v>
+      </c>
+      <c r="H632" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="633" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A633" t="s">
+        <v>242</v>
+      </c>
+      <c r="B633" t="s">
+        <v>243</v>
+      </c>
+      <c r="C633" t="s">
+        <v>268</v>
+      </c>
+      <c r="D633" t="s">
+        <v>269</v>
+      </c>
+      <c r="E633" t="s">
+        <v>48</v>
+      </c>
+      <c r="F633" t="s">
+        <v>13</v>
+      </c>
+      <c r="H633" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="634" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A634" t="s">
+        <v>242</v>
+      </c>
+      <c r="B634" t="s">
+        <v>243</v>
+      </c>
+      <c r="C634" t="s">
+        <v>270</v>
+      </c>
+      <c r="D634" t="s">
+        <v>271</v>
+      </c>
+      <c r="E634" t="s">
+        <v>48</v>
+      </c>
+      <c r="F634" t="s">
+        <v>13</v>
+      </c>
+      <c r="H634" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="635" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A635" t="s">
+        <v>242</v>
+      </c>
+      <c r="B635" t="s">
+        <v>243</v>
+      </c>
+      <c r="C635" t="s">
+        <v>272</v>
+      </c>
+      <c r="D635" t="s">
+        <v>273</v>
+      </c>
+      <c r="E635" t="s">
+        <v>48</v>
+      </c>
+      <c r="F635" t="s">
+        <v>13</v>
+      </c>
+      <c r="H635" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="636" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A636" t="s">
+        <v>242</v>
+      </c>
+      <c r="B636" t="s">
+        <v>243</v>
+      </c>
+      <c r="C636" t="s">
+        <v>274</v>
+      </c>
+      <c r="D636" t="s">
+        <v>275</v>
+      </c>
+      <c r="E636" t="s">
+        <v>48</v>
+      </c>
+      <c r="F636" t="s">
+        <v>13</v>
+      </c>
+      <c r="H636" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="637" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A637" t="s">
+        <v>242</v>
+      </c>
+      <c r="B637" t="s">
+        <v>243</v>
+      </c>
+      <c r="C637" t="s">
+        <v>276</v>
+      </c>
+      <c r="D637" t="s">
+        <v>277</v>
+      </c>
+      <c r="E637" t="s">
+        <v>48</v>
+      </c>
+      <c r="F637" t="s">
+        <v>13</v>
+      </c>
+      <c r="H637" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="638" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A638" t="s">
+        <v>242</v>
+      </c>
+      <c r="B638" t="s">
+        <v>243</v>
+      </c>
+      <c r="C638" t="s">
+        <v>278</v>
+      </c>
+      <c r="D638" t="s">
+        <v>279</v>
+      </c>
+      <c r="E638" t="s">
+        <v>48</v>
+      </c>
+      <c r="F638" t="s">
+        <v>13</v>
+      </c>
+      <c r="H638" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="639" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A639" t="s">
+        <v>242</v>
+      </c>
+      <c r="B639" t="s">
+        <v>243</v>
+      </c>
+      <c r="C639" t="s">
+        <v>280</v>
+      </c>
+      <c r="D639" t="s">
+        <v>281</v>
+      </c>
+      <c r="E639" t="s">
+        <v>48</v>
+      </c>
+      <c r="F639" t="s">
+        <v>13</v>
+      </c>
+      <c r="H639" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="640" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A640" t="s">
+        <v>244</v>
+      </c>
+      <c r="B640" t="s">
+        <v>245</v>
+      </c>
+      <c r="C640" t="s">
+        <v>246</v>
+      </c>
+      <c r="D640" t="s">
+        <v>247</v>
+      </c>
+      <c r="E640" t="s">
+        <v>48</v>
+      </c>
+      <c r="F640" t="s">
+        <v>13</v>
+      </c>
+      <c r="H640" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="641" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A641" t="s">
+        <v>244</v>
+      </c>
+      <c r="B641" t="s">
+        <v>245</v>
+      </c>
+      <c r="C641" t="s">
+        <v>248</v>
+      </c>
+      <c r="D641" t="s">
+        <v>249</v>
+      </c>
+      <c r="E641" t="s">
+        <v>48</v>
+      </c>
+      <c r="F641" t="s">
+        <v>13</v>
+      </c>
+      <c r="H641" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="642" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A642" t="s">
+        <v>244</v>
+      </c>
+      <c r="B642" t="s">
+        <v>245</v>
+      </c>
+      <c r="C642" t="s">
+        <v>250</v>
+      </c>
+      <c r="D642" t="s">
+        <v>251</v>
+      </c>
+      <c r="E642" t="s">
+        <v>48</v>
+      </c>
+      <c r="F642" t="s">
+        <v>13</v>
+      </c>
+      <c r="H642" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="643" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A643" t="s">
+        <v>244</v>
+      </c>
+      <c r="B643" t="s">
+        <v>245</v>
+      </c>
+      <c r="C643" t="s">
+        <v>252</v>
+      </c>
+      <c r="D643" t="s">
+        <v>253</v>
+      </c>
+      <c r="E643" t="s">
+        <v>48</v>
+      </c>
+      <c r="F643" t="s">
+        <v>13</v>
+      </c>
+      <c r="H643" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="644" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A644" t="s">
+        <v>244</v>
+      </c>
+      <c r="B644" t="s">
+        <v>245</v>
+      </c>
+      <c r="C644" t="s">
+        <v>254</v>
+      </c>
+      <c r="D644" t="s">
+        <v>255</v>
+      </c>
+      <c r="E644" t="s">
+        <v>48</v>
+      </c>
+      <c r="F644" t="s">
+        <v>13</v>
+      </c>
+      <c r="H644" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="645" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A645" t="s">
+        <v>244</v>
+      </c>
+      <c r="B645" t="s">
+        <v>245</v>
+      </c>
+      <c r="C645" t="s">
+        <v>256</v>
+      </c>
+      <c r="D645" t="s">
+        <v>257</v>
+      </c>
+      <c r="E645" t="s">
+        <v>48</v>
+      </c>
+      <c r="F645" t="s">
+        <v>13</v>
+      </c>
+      <c r="H645" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="646" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A646" t="s">
+        <v>244</v>
+      </c>
+      <c r="B646" t="s">
+        <v>245</v>
+      </c>
+      <c r="C646" t="s">
+        <v>258</v>
+      </c>
+      <c r="D646" t="s">
+        <v>259</v>
+      </c>
+      <c r="E646" t="s">
+        <v>48</v>
+      </c>
+      <c r="F646" t="s">
+        <v>13</v>
+      </c>
+      <c r="H646" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="647" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A647" t="s">
+        <v>244</v>
+      </c>
+      <c r="B647" t="s">
+        <v>245</v>
+      </c>
+      <c r="C647" t="s">
+        <v>260</v>
+      </c>
+      <c r="D647" t="s">
+        <v>261</v>
+      </c>
+      <c r="E647" t="s">
+        <v>48</v>
+      </c>
+      <c r="F647" t="s">
+        <v>13</v>
+      </c>
+      <c r="H647" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="648" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A648" t="s">
+        <v>244</v>
+      </c>
+      <c r="B648" t="s">
+        <v>245</v>
+      </c>
+      <c r="C648" t="s">
+        <v>262</v>
+      </c>
+      <c r="D648" t="s">
+        <v>263</v>
+      </c>
+      <c r="E648" t="s">
+        <v>48</v>
+      </c>
+      <c r="F648" t="s">
+        <v>13</v>
+      </c>
+      <c r="H648" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="649" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A649" t="s">
+        <v>244</v>
+      </c>
+      <c r="B649" t="s">
+        <v>245</v>
+      </c>
+      <c r="C649" t="s">
+        <v>264</v>
+      </c>
+      <c r="D649" t="s">
+        <v>265</v>
+      </c>
+      <c r="E649" t="s">
+        <v>48</v>
+      </c>
+      <c r="F649" t="s">
+        <v>13</v>
+      </c>
+      <c r="H649" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="650" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A650" t="s">
+        <v>244</v>
+      </c>
+      <c r="B650" t="s">
+        <v>245</v>
+      </c>
+      <c r="C650" t="s">
+        <v>266</v>
+      </c>
+      <c r="D650" t="s">
+        <v>267</v>
+      </c>
+      <c r="E650" t="s">
+        <v>48</v>
+      </c>
+      <c r="F650" t="s">
+        <v>13</v>
+      </c>
+      <c r="H650" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="651" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A651" t="s">
+        <v>244</v>
+      </c>
+      <c r="B651" t="s">
+        <v>245</v>
+      </c>
+      <c r="C651" t="s">
+        <v>268</v>
+      </c>
+      <c r="D651" t="s">
+        <v>269</v>
+      </c>
+      <c r="E651" t="s">
+        <v>48</v>
+      </c>
+      <c r="F651" t="s">
+        <v>13</v>
+      </c>
+      <c r="H651" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="652" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A652" t="s">
+        <v>244</v>
+      </c>
+      <c r="B652" t="s">
+        <v>245</v>
+      </c>
+      <c r="C652" t="s">
+        <v>270</v>
+      </c>
+      <c r="D652" t="s">
+        <v>271</v>
+      </c>
+      <c r="E652" t="s">
+        <v>48</v>
+      </c>
+      <c r="F652" t="s">
+        <v>13</v>
+      </c>
+      <c r="H652" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="653" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A653" t="s">
+        <v>244</v>
+      </c>
+      <c r="B653" t="s">
+        <v>245</v>
+      </c>
+      <c r="C653" t="s">
+        <v>272</v>
+      </c>
+      <c r="D653" t="s">
+        <v>273</v>
+      </c>
+      <c r="E653" t="s">
+        <v>48</v>
+      </c>
+      <c r="F653" t="s">
+        <v>13</v>
+      </c>
+      <c r="H653" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="654" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A654" t="s">
+        <v>244</v>
+      </c>
+      <c r="B654" t="s">
+        <v>245</v>
+      </c>
+      <c r="C654" t="s">
+        <v>274</v>
+      </c>
+      <c r="D654" t="s">
+        <v>275</v>
+      </c>
+      <c r="E654" t="s">
+        <v>48</v>
+      </c>
+      <c r="F654" t="s">
+        <v>13</v>
+      </c>
+      <c r="H654" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="655" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A655" t="s">
+        <v>244</v>
+      </c>
+      <c r="B655" t="s">
+        <v>245</v>
+      </c>
+      <c r="C655" t="s">
+        <v>276</v>
+      </c>
+      <c r="D655" t="s">
+        <v>277</v>
+      </c>
+      <c r="E655" t="s">
+        <v>48</v>
+      </c>
+      <c r="F655" t="s">
+        <v>13</v>
+      </c>
+      <c r="H655" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="656" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A656" t="s">
+        <v>244</v>
+      </c>
+      <c r="B656" t="s">
+        <v>245</v>
+      </c>
+      <c r="C656" t="s">
+        <v>278</v>
+      </c>
+      <c r="D656" t="s">
+        <v>279</v>
+      </c>
+      <c r="E656" t="s">
+        <v>48</v>
+      </c>
+      <c r="F656" t="s">
+        <v>13</v>
+      </c>
+      <c r="H656" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="657" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A657" t="s">
+        <v>244</v>
+      </c>
+      <c r="B657" t="s">
+        <v>245</v>
+      </c>
+      <c r="C657" t="s">
+        <v>280</v>
+      </c>
+      <c r="D657" t="s">
+        <v>281</v>
+      </c>
+      <c r="E657" t="s">
+        <v>48</v>
+      </c>
+      <c r="F657" t="s">
+        <v>13</v>
+      </c>
+      <c r="H657" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="658" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A658" t="s">
+        <v>246</v>
+      </c>
+      <c r="B658" t="s">
+        <v>247</v>
+      </c>
+      <c r="C658" t="s">
+        <v>248</v>
+      </c>
+      <c r="D658" t="s">
+        <v>249</v>
+      </c>
+      <c r="E658" t="s">
+        <v>63</v>
+      </c>
+      <c r="F658" t="s">
+        <v>13</v>
+      </c>
+      <c r="H658" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="659" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A659" t="s">
+        <v>246</v>
+      </c>
+      <c r="B659" t="s">
+        <v>247</v>
+      </c>
+      <c r="C659" t="s">
+        <v>250</v>
+      </c>
+      <c r="D659" t="s">
+        <v>251</v>
+      </c>
+      <c r="E659" t="s">
+        <v>63</v>
+      </c>
+      <c r="F659" t="s">
+        <v>13</v>
+      </c>
+      <c r="H659" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="660" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A660" t="s">
+        <v>246</v>
+      </c>
+      <c r="B660" t="s">
+        <v>247</v>
+      </c>
+      <c r="C660" t="s">
+        <v>252</v>
+      </c>
+      <c r="D660" t="s">
+        <v>253</v>
+      </c>
+      <c r="E660" t="s">
+        <v>63</v>
+      </c>
+      <c r="F660" t="s">
+        <v>13</v>
+      </c>
+      <c r="H660" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="661" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A661" t="s">
+        <v>246</v>
+      </c>
+      <c r="B661" t="s">
+        <v>247</v>
+      </c>
+      <c r="C661" t="s">
+        <v>254</v>
+      </c>
+      <c r="D661" t="s">
+        <v>255</v>
+      </c>
+      <c r="E661" t="s">
+        <v>63</v>
+      </c>
+      <c r="F661" t="s">
+        <v>13</v>
+      </c>
+      <c r="H661" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="662" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A662" t="s">
+        <v>246</v>
+      </c>
+      <c r="B662" t="s">
+        <v>247</v>
+      </c>
+      <c r="C662" t="s">
+        <v>256</v>
+      </c>
+      <c r="D662" t="s">
+        <v>257</v>
+      </c>
+      <c r="E662" t="s">
+        <v>63</v>
+      </c>
+      <c r="F662" t="s">
+        <v>13</v>
+      </c>
+      <c r="H662" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="663" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A663" t="s">
+        <v>246</v>
+      </c>
+      <c r="B663" t="s">
+        <v>247</v>
+      </c>
+      <c r="C663" t="s">
+        <v>258</v>
+      </c>
+      <c r="D663" t="s">
+        <v>259</v>
+      </c>
+      <c r="E663" t="s">
+        <v>63</v>
+      </c>
+      <c r="F663" t="s">
+        <v>13</v>
+      </c>
+      <c r="H663" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="664" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A664" t="s">
+        <v>246</v>
+      </c>
+      <c r="B664" t="s">
+        <v>247</v>
+      </c>
+      <c r="C664" t="s">
+        <v>260</v>
+      </c>
+      <c r="D664" t="s">
+        <v>261</v>
+      </c>
+      <c r="E664" t="s">
+        <v>63</v>
+      </c>
+      <c r="F664" t="s">
+        <v>13</v>
+      </c>
+      <c r="H664" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="665" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A665" t="s">
+        <v>246</v>
+      </c>
+      <c r="B665" t="s">
+        <v>247</v>
+      </c>
+      <c r="C665" t="s">
+        <v>262</v>
+      </c>
+      <c r="D665" t="s">
+        <v>263</v>
+      </c>
+      <c r="E665" t="s">
+        <v>63</v>
+      </c>
+      <c r="F665" t="s">
+        <v>13</v>
+      </c>
+      <c r="H665" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="666" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A666" t="s">
+        <v>246</v>
+      </c>
+      <c r="B666" t="s">
+        <v>247</v>
+      </c>
+      <c r="C666" t="s">
+        <v>264</v>
+      </c>
+      <c r="D666" t="s">
+        <v>265</v>
+      </c>
+      <c r="E666" t="s">
+        <v>63</v>
+      </c>
+      <c r="F666" t="s">
+        <v>13</v>
+      </c>
+      <c r="H666" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="667" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A667" t="s">
+        <v>246</v>
+      </c>
+      <c r="B667" t="s">
+        <v>247</v>
+      </c>
+      <c r="C667" t="s">
+        <v>266</v>
+      </c>
+      <c r="D667" t="s">
+        <v>267</v>
+      </c>
+      <c r="E667" t="s">
+        <v>63</v>
+      </c>
+      <c r="F667" t="s">
+        <v>13</v>
+      </c>
+      <c r="H667" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="668" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A668" t="s">
+        <v>246</v>
+      </c>
+      <c r="B668" t="s">
+        <v>247</v>
+      </c>
+      <c r="C668" t="s">
+        <v>268</v>
+      </c>
+      <c r="D668" t="s">
+        <v>269</v>
+      </c>
+      <c r="E668" t="s">
+        <v>63</v>
+      </c>
+      <c r="F668" t="s">
+        <v>13</v>
+      </c>
+      <c r="H668" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="669" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A669" t="s">
+        <v>246</v>
+      </c>
+      <c r="B669" t="s">
+        <v>247</v>
+      </c>
+      <c r="C669" t="s">
+        <v>270</v>
+      </c>
+      <c r="D669" t="s">
+        <v>271</v>
+      </c>
+      <c r="E669" t="s">
+        <v>63</v>
+      </c>
+      <c r="F669" t="s">
+        <v>13</v>
+      </c>
+      <c r="H669" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="670" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A670" t="s">
+        <v>246</v>
+      </c>
+      <c r="B670" t="s">
+        <v>247</v>
+      </c>
+      <c r="C670" t="s">
+        <v>272</v>
+      </c>
+      <c r="D670" t="s">
+        <v>273</v>
+      </c>
+      <c r="E670" t="s">
+        <v>63</v>
+      </c>
+      <c r="F670" t="s">
+        <v>13</v>
+      </c>
+      <c r="H670" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="671" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A671" t="s">
+        <v>246</v>
+      </c>
+      <c r="B671" t="s">
+        <v>247</v>
+      </c>
+      <c r="C671" t="s">
+        <v>274</v>
+      </c>
+      <c r="D671" t="s">
+        <v>275</v>
+      </c>
+      <c r="E671" t="s">
+        <v>63</v>
+      </c>
+      <c r="F671" t="s">
+        <v>13</v>
+      </c>
+      <c r="H671" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="672" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A672" t="s">
+        <v>246</v>
+      </c>
+      <c r="B672" t="s">
+        <v>247</v>
+      </c>
+      <c r="C672" t="s">
+        <v>276</v>
+      </c>
+      <c r="D672" t="s">
+        <v>277</v>
+      </c>
+      <c r="E672" t="s">
+        <v>63</v>
+      </c>
+      <c r="F672" t="s">
+        <v>13</v>
+      </c>
+      <c r="H672" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="673" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A673" t="s">
+        <v>246</v>
+      </c>
+      <c r="B673" t="s">
+        <v>247</v>
+      </c>
+      <c r="C673" t="s">
+        <v>278</v>
+      </c>
+      <c r="D673" t="s">
+        <v>279</v>
+      </c>
+      <c r="E673" t="s">
+        <v>63</v>
+      </c>
+      <c r="F673" t="s">
+        <v>13</v>
+      </c>
+      <c r="H673" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="674" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A674" t="s">
+        <v>246</v>
+      </c>
+      <c r="B674" t="s">
+        <v>247</v>
+      </c>
+      <c r="C674" t="s">
+        <v>280</v>
+      </c>
+      <c r="D674" t="s">
+        <v>281</v>
+      </c>
+      <c r="E674" t="s">
+        <v>63</v>
+      </c>
+      <c r="F674" t="s">
+        <v>13</v>
+      </c>
+      <c r="H674" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="675" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A675" t="s">
+        <v>248</v>
+      </c>
+      <c r="B675" t="s">
+        <v>249</v>
+      </c>
+      <c r="C675" t="s">
+        <v>250</v>
+      </c>
+      <c r="D675" t="s">
+        <v>251</v>
+      </c>
+      <c r="E675" t="s">
+        <v>48</v>
+      </c>
+      <c r="F675" t="s">
+        <v>13</v>
+      </c>
+      <c r="H675" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="676" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A676" t="s">
+        <v>248</v>
+      </c>
+      <c r="B676" t="s">
+        <v>249</v>
+      </c>
+      <c r="C676" t="s">
+        <v>252</v>
+      </c>
+      <c r="D676" t="s">
+        <v>253</v>
+      </c>
+      <c r="E676" t="s">
+        <v>48</v>
+      </c>
+      <c r="F676" t="s">
+        <v>13</v>
+      </c>
+      <c r="H676" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="677" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A677" t="s">
+        <v>248</v>
+      </c>
+      <c r="B677" t="s">
+        <v>249</v>
+      </c>
+      <c r="C677" t="s">
+        <v>254</v>
+      </c>
+      <c r="D677" t="s">
+        <v>255</v>
+      </c>
+      <c r="E677" t="s">
+        <v>48</v>
+      </c>
+      <c r="F677" t="s">
+        <v>13</v>
+      </c>
+      <c r="H677" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="678" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A678" t="s">
+        <v>248</v>
+      </c>
+      <c r="B678" t="s">
+        <v>249</v>
+      </c>
+      <c r="C678" t="s">
+        <v>256</v>
+      </c>
+      <c r="D678" t="s">
+        <v>257</v>
+      </c>
+      <c r="E678" t="s">
+        <v>48</v>
+      </c>
+      <c r="F678" t="s">
+        <v>13</v>
+      </c>
+      <c r="H678" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="679" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A679" t="s">
+        <v>248</v>
+      </c>
+      <c r="B679" t="s">
+        <v>249</v>
+      </c>
+      <c r="C679" t="s">
+        <v>258</v>
+      </c>
+      <c r="D679" t="s">
+        <v>259</v>
+      </c>
+      <c r="E679" t="s">
+        <v>48</v>
+      </c>
+      <c r="F679" t="s">
+        <v>13</v>
+      </c>
+      <c r="H679" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="680" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A680" t="s">
+        <v>248</v>
+      </c>
+      <c r="B680" t="s">
+        <v>249</v>
+      </c>
+      <c r="C680" t="s">
+        <v>260</v>
+      </c>
+      <c r="D680" t="s">
+        <v>261</v>
+      </c>
+      <c r="E680" t="s">
+        <v>48</v>
+      </c>
+      <c r="F680" t="s">
+        <v>13</v>
+      </c>
+      <c r="H680" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="681" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A681" t="s">
+        <v>248</v>
+      </c>
+      <c r="B681" t="s">
+        <v>249</v>
+      </c>
+      <c r="C681" t="s">
+        <v>262</v>
+      </c>
+      <c r="D681" t="s">
+        <v>263</v>
+      </c>
+      <c r="E681" t="s">
+        <v>48</v>
+      </c>
+      <c r="F681" t="s">
+        <v>13</v>
+      </c>
+      <c r="H681" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="682" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A682" t="s">
+        <v>248</v>
+      </c>
+      <c r="B682" t="s">
+        <v>249</v>
+      </c>
+      <c r="C682" t="s">
+        <v>264</v>
+      </c>
+      <c r="D682" t="s">
+        <v>265</v>
+      </c>
+      <c r="E682" t="s">
+        <v>48</v>
+      </c>
+      <c r="F682" t="s">
+        <v>13</v>
+      </c>
+      <c r="H682" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="683" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A683" t="s">
+        <v>248</v>
+      </c>
+      <c r="B683" t="s">
+        <v>249</v>
+      </c>
+      <c r="C683" t="s">
+        <v>266</v>
+      </c>
+      <c r="D683" t="s">
+        <v>267</v>
+      </c>
+      <c r="E683" t="s">
+        <v>48</v>
+      </c>
+      <c r="F683" t="s">
+        <v>13</v>
+      </c>
+      <c r="H683" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="684" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A684" t="s">
+        <v>248</v>
+      </c>
+      <c r="B684" t="s">
+        <v>249</v>
+      </c>
+      <c r="C684" t="s">
+        <v>268</v>
+      </c>
+      <c r="D684" t="s">
+        <v>269</v>
+      </c>
+      <c r="E684" t="s">
+        <v>48</v>
+      </c>
+      <c r="F684" t="s">
+        <v>13</v>
+      </c>
+      <c r="H684" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="685" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A685" t="s">
+        <v>248</v>
+      </c>
+      <c r="B685" t="s">
+        <v>249</v>
+      </c>
+      <c r="C685" t="s">
+        <v>270</v>
+      </c>
+      <c r="D685" t="s">
+        <v>271</v>
+      </c>
+      <c r="E685" t="s">
+        <v>48</v>
+      </c>
+      <c r="F685" t="s">
+        <v>13</v>
+      </c>
+      <c r="H685" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="686" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A686" t="s">
+        <v>248</v>
+      </c>
+      <c r="B686" t="s">
+        <v>249</v>
+      </c>
+      <c r="C686" t="s">
+        <v>272</v>
+      </c>
+      <c r="D686" t="s">
+        <v>273</v>
+      </c>
+      <c r="E686" t="s">
+        <v>48</v>
+      </c>
+      <c r="F686" t="s">
+        <v>13</v>
+      </c>
+      <c r="H686" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="687" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A687" t="s">
+        <v>248</v>
+      </c>
+      <c r="B687" t="s">
+        <v>249</v>
+      </c>
+      <c r="C687" t="s">
+        <v>274</v>
+      </c>
+      <c r="D687" t="s">
+        <v>275</v>
+      </c>
+      <c r="E687" t="s">
+        <v>48</v>
+      </c>
+      <c r="F687" t="s">
+        <v>13</v>
+      </c>
+      <c r="H687" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="688" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A688" t="s">
+        <v>248</v>
+      </c>
+      <c r="B688" t="s">
+        <v>249</v>
+      </c>
+      <c r="C688" t="s">
+        <v>276</v>
+      </c>
+      <c r="D688" t="s">
+        <v>277</v>
+      </c>
+      <c r="E688" t="s">
+        <v>48</v>
+      </c>
+      <c r="F688" t="s">
+        <v>13</v>
+      </c>
+      <c r="H688" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="689" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A689" t="s">
+        <v>248</v>
+      </c>
+      <c r="B689" t="s">
+        <v>249</v>
+      </c>
+      <c r="C689" t="s">
+        <v>278</v>
+      </c>
+      <c r="D689" t="s">
+        <v>279</v>
+      </c>
+      <c r="E689" t="s">
+        <v>48</v>
+      </c>
+      <c r="F689" t="s">
+        <v>13</v>
+      </c>
+      <c r="H689" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="690" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A690" t="s">
+        <v>248</v>
+      </c>
+      <c r="B690" t="s">
+        <v>249</v>
+      </c>
+      <c r="C690" t="s">
+        <v>280</v>
+      </c>
+      <c r="D690" t="s">
+        <v>281</v>
+      </c>
+      <c r="E690" t="s">
+        <v>48</v>
+      </c>
+      <c r="F690" t="s">
+        <v>13</v>
+      </c>
+      <c r="H690" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="691" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A691" t="s">
+        <v>250</v>
+      </c>
+      <c r="B691" t="s">
+        <v>251</v>
+      </c>
+      <c r="C691" t="s">
+        <v>252</v>
+      </c>
+      <c r="D691" t="s">
+        <v>253</v>
+      </c>
+      <c r="E691" t="s">
+        <v>63</v>
+      </c>
+      <c r="F691" t="s">
+        <v>13</v>
+      </c>
+      <c r="H691" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="692" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A692" t="s">
+        <v>250</v>
+      </c>
+      <c r="B692" t="s">
+        <v>251</v>
+      </c>
+      <c r="C692" t="s">
+        <v>254</v>
+      </c>
+      <c r="D692" t="s">
+        <v>255</v>
+      </c>
+      <c r="E692" t="s">
+        <v>63</v>
+      </c>
+      <c r="F692" t="s">
+        <v>13</v>
+      </c>
+      <c r="H692" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="693" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A693" t="s">
+        <v>250</v>
+      </c>
+      <c r="B693" t="s">
+        <v>251</v>
+      </c>
+      <c r="C693" t="s">
+        <v>256</v>
+      </c>
+      <c r="D693" t="s">
+        <v>257</v>
+      </c>
+      <c r="E693" t="s">
+        <v>63</v>
+      </c>
+      <c r="F693" t="s">
+        <v>13</v>
+      </c>
+      <c r="H693" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="694" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A694" t="s">
+        <v>250</v>
+      </c>
+      <c r="B694" t="s">
+        <v>251</v>
+      </c>
+      <c r="C694" t="s">
+        <v>258</v>
+      </c>
+      <c r="D694" t="s">
+        <v>259</v>
+      </c>
+      <c r="E694" t="s">
+        <v>63</v>
+      </c>
+      <c r="F694" t="s">
+        <v>13</v>
+      </c>
+      <c r="H694" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="695" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A695" t="s">
+        <v>250</v>
+      </c>
+      <c r="B695" t="s">
+        <v>251</v>
+      </c>
+      <c r="C695" t="s">
+        <v>260</v>
+      </c>
+      <c r="D695" t="s">
+        <v>261</v>
+      </c>
+      <c r="E695" t="s">
+        <v>63</v>
+      </c>
+      <c r="F695" t="s">
+        <v>13</v>
+      </c>
+      <c r="H695" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="696" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A696" t="s">
+        <v>250</v>
+      </c>
+      <c r="B696" t="s">
+        <v>251</v>
+      </c>
+      <c r="C696" t="s">
+        <v>262</v>
+      </c>
+      <c r="D696" t="s">
+        <v>263</v>
+      </c>
+      <c r="E696" t="s">
+        <v>63</v>
+      </c>
+      <c r="F696" t="s">
+        <v>13</v>
+      </c>
+      <c r="H696" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="697" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A697" t="s">
+        <v>250</v>
+      </c>
+      <c r="B697" t="s">
+        <v>251</v>
+      </c>
+      <c r="C697" t="s">
+        <v>264</v>
+      </c>
+      <c r="D697" t="s">
+        <v>265</v>
+      </c>
+      <c r="E697" t="s">
+        <v>63</v>
+      </c>
+      <c r="F697" t="s">
+        <v>13</v>
+      </c>
+      <c r="H697" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="698" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A698" t="s">
+        <v>250</v>
+      </c>
+      <c r="B698" t="s">
+        <v>251</v>
+      </c>
+      <c r="C698" t="s">
+        <v>266</v>
+      </c>
+      <c r="D698" t="s">
+        <v>267</v>
+      </c>
+      <c r="E698" t="s">
+        <v>63</v>
+      </c>
+      <c r="F698" t="s">
+        <v>13</v>
+      </c>
+      <c r="H698" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="699" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A699" t="s">
+        <v>250</v>
+      </c>
+      <c r="B699" t="s">
+        <v>251</v>
+      </c>
+      <c r="C699" t="s">
+        <v>268</v>
+      </c>
+      <c r="D699" t="s">
+        <v>269</v>
+      </c>
+      <c r="E699" t="s">
+        <v>63</v>
+      </c>
+      <c r="F699" t="s">
+        <v>13</v>
+      </c>
+      <c r="H699" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="700" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A700" t="s">
+        <v>250</v>
+      </c>
+      <c r="B700" t="s">
+        <v>251</v>
+      </c>
+      <c r="C700" t="s">
+        <v>270</v>
+      </c>
+      <c r="D700" t="s">
+        <v>271</v>
+      </c>
+      <c r="E700" t="s">
+        <v>63</v>
+      </c>
+      <c r="F700" t="s">
+        <v>13</v>
+      </c>
+      <c r="H700" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="701" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A701" t="s">
+        <v>250</v>
+      </c>
+      <c r="B701" t="s">
+        <v>251</v>
+      </c>
+      <c r="C701" t="s">
+        <v>272</v>
+      </c>
+      <c r="D701" t="s">
+        <v>273</v>
+      </c>
+      <c r="E701" t="s">
+        <v>63</v>
+      </c>
+      <c r="F701" t="s">
+        <v>13</v>
+      </c>
+      <c r="H701" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="702" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A702" t="s">
+        <v>250</v>
+      </c>
+      <c r="B702" t="s">
+        <v>251</v>
+      </c>
+      <c r="C702" t="s">
+        <v>274</v>
+      </c>
+      <c r="D702" t="s">
+        <v>275</v>
+      </c>
+      <c r="E702" t="s">
+        <v>63</v>
+      </c>
+      <c r="F702" t="s">
+        <v>13</v>
+      </c>
+      <c r="H702" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="703" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A703" t="s">
+        <v>250</v>
+      </c>
+      <c r="B703" t="s">
+        <v>251</v>
+      </c>
+      <c r="C703" t="s">
+        <v>276</v>
+      </c>
+      <c r="D703" t="s">
+        <v>277</v>
+      </c>
+      <c r="E703" t="s">
+        <v>63</v>
+      </c>
+      <c r="F703" t="s">
+        <v>13</v>
+      </c>
+      <c r="H703" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="704" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A704" t="s">
+        <v>250</v>
+      </c>
+      <c r="B704" t="s">
+        <v>251</v>
+      </c>
+      <c r="C704" t="s">
+        <v>278</v>
+      </c>
+      <c r="D704" t="s">
+        <v>279</v>
+      </c>
+      <c r="E704" t="s">
+        <v>63</v>
+      </c>
+      <c r="F704" t="s">
+        <v>13</v>
+      </c>
+      <c r="H704" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="705" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A705" t="s">
+        <v>250</v>
+      </c>
+      <c r="B705" t="s">
+        <v>251</v>
+      </c>
+      <c r="C705" t="s">
+        <v>280</v>
+      </c>
+      <c r="D705" t="s">
+        <v>281</v>
+      </c>
+      <c r="E705" t="s">
+        <v>63</v>
+      </c>
+      <c r="F705" t="s">
+        <v>13</v>
+      </c>
+      <c r="H705" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="706" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A706" t="s">
+        <v>252</v>
+      </c>
+      <c r="B706" t="s">
+        <v>253</v>
+      </c>
+      <c r="C706" t="s">
+        <v>254</v>
+      </c>
+      <c r="D706" t="s">
+        <v>255</v>
+      </c>
+      <c r="E706" t="s">
+        <v>63</v>
+      </c>
+      <c r="F706" t="s">
+        <v>13</v>
+      </c>
+      <c r="H706" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="707" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A707" t="s">
+        <v>252</v>
+      </c>
+      <c r="B707" t="s">
+        <v>253</v>
+      </c>
+      <c r="C707" t="s">
+        <v>256</v>
+      </c>
+      <c r="D707" t="s">
+        <v>257</v>
+      </c>
+      <c r="E707" t="s">
+        <v>63</v>
+      </c>
+      <c r="F707" t="s">
+        <v>13</v>
+      </c>
+      <c r="H707" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="708" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A708" t="s">
+        <v>252</v>
+      </c>
+      <c r="B708" t="s">
+        <v>253</v>
+      </c>
+      <c r="C708" t="s">
+        <v>258</v>
+      </c>
+      <c r="D708" t="s">
+        <v>259</v>
+      </c>
+      <c r="E708" t="s">
+        <v>63</v>
+      </c>
+      <c r="F708" t="s">
+        <v>13</v>
+      </c>
+      <c r="H708" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="709" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A709" t="s">
+        <v>252</v>
+      </c>
+      <c r="B709" t="s">
+        <v>253</v>
+      </c>
+      <c r="C709" t="s">
+        <v>260</v>
+      </c>
+      <c r="D709" t="s">
+        <v>261</v>
+      </c>
+      <c r="E709" t="s">
+        <v>63</v>
+      </c>
+      <c r="F709" t="s">
+        <v>13</v>
+      </c>
+      <c r="H709" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="710" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A710" t="s">
+        <v>252</v>
+      </c>
+      <c r="B710" t="s">
+        <v>253</v>
+      </c>
+      <c r="C710" t="s">
+        <v>262</v>
+      </c>
+      <c r="D710" t="s">
+        <v>263</v>
+      </c>
+      <c r="E710" t="s">
+        <v>63</v>
+      </c>
+      <c r="F710" t="s">
+        <v>13</v>
+      </c>
+      <c r="H710" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="711" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A711" t="s">
+        <v>252</v>
+      </c>
+      <c r="B711" t="s">
+        <v>253</v>
+      </c>
+      <c r="C711" t="s">
+        <v>264</v>
+      </c>
+      <c r="D711" t="s">
+        <v>265</v>
+      </c>
+      <c r="E711" t="s">
+        <v>63</v>
+      </c>
+      <c r="F711" t="s">
+        <v>13</v>
+      </c>
+      <c r="H711" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="712" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A712" t="s">
+        <v>252</v>
+      </c>
+      <c r="B712" t="s">
+        <v>253</v>
+      </c>
+      <c r="C712" t="s">
+        <v>266</v>
+      </c>
+      <c r="D712" t="s">
+        <v>267</v>
+      </c>
+      <c r="E712" t="s">
+        <v>63</v>
+      </c>
+      <c r="F712" t="s">
+        <v>13</v>
+      </c>
+      <c r="H712" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="713" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A713" t="s">
+        <v>252</v>
+      </c>
+      <c r="B713" t="s">
+        <v>253</v>
+      </c>
+      <c r="C713" t="s">
+        <v>268</v>
+      </c>
+      <c r="D713" t="s">
+        <v>269</v>
+      </c>
+      <c r="E713" t="s">
+        <v>63</v>
+      </c>
+      <c r="F713" t="s">
+        <v>13</v>
+      </c>
+      <c r="H713" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="714" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A714" t="s">
+        <v>252</v>
+      </c>
+      <c r="B714" t="s">
+        <v>253</v>
+      </c>
+      <c r="C714" t="s">
+        <v>270</v>
+      </c>
+      <c r="D714" t="s">
+        <v>271</v>
+      </c>
+      <c r="E714" t="s">
+        <v>63</v>
+      </c>
+      <c r="F714" t="s">
+        <v>13</v>
+      </c>
+      <c r="H714" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="715" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A715" t="s">
+        <v>252</v>
+      </c>
+      <c r="B715" t="s">
+        <v>253</v>
+      </c>
+      <c r="C715" t="s">
+        <v>272</v>
+      </c>
+      <c r="D715" t="s">
+        <v>273</v>
+      </c>
+      <c r="E715" t="s">
+        <v>63</v>
+      </c>
+      <c r="F715" t="s">
+        <v>13</v>
+      </c>
+      <c r="H715" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="716" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A716" t="s">
+        <v>252</v>
+      </c>
+      <c r="B716" t="s">
+        <v>253</v>
+      </c>
+      <c r="C716" t="s">
+        <v>274</v>
+      </c>
+      <c r="D716" t="s">
+        <v>275</v>
+      </c>
+      <c r="E716" t="s">
+        <v>63</v>
+      </c>
+      <c r="F716" t="s">
+        <v>13</v>
+      </c>
+      <c r="H716" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="717" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A717" t="s">
+        <v>252</v>
+      </c>
+      <c r="B717" t="s">
+        <v>253</v>
+      </c>
+      <c r="C717" t="s">
+        <v>276</v>
+      </c>
+      <c r="D717" t="s">
+        <v>277</v>
+      </c>
+      <c r="E717" t="s">
+        <v>63</v>
+      </c>
+      <c r="F717" t="s">
+        <v>13</v>
+      </c>
+      <c r="H717" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="718" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A718" t="s">
+        <v>252</v>
+      </c>
+      <c r="B718" t="s">
+        <v>253</v>
+      </c>
+      <c r="C718" t="s">
+        <v>278</v>
+      </c>
+      <c r="D718" t="s">
+        <v>279</v>
+      </c>
+      <c r="E718" t="s">
+        <v>63</v>
+      </c>
+      <c r="F718" t="s">
+        <v>13</v>
+      </c>
+      <c r="H718" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="719" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A719" t="s">
+        <v>252</v>
+      </c>
+      <c r="B719" t="s">
+        <v>253</v>
+      </c>
+      <c r="C719" t="s">
+        <v>280</v>
+      </c>
+      <c r="D719" t="s">
+        <v>281</v>
+      </c>
+      <c r="E719" t="s">
+        <v>63</v>
+      </c>
+      <c r="F719" t="s">
+        <v>13</v>
+      </c>
+      <c r="H719" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="720" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A720" t="s">
+        <v>254</v>
+      </c>
+      <c r="B720" t="s">
+        <v>255</v>
+      </c>
+      <c r="C720" t="s">
+        <v>256</v>
+      </c>
+      <c r="D720" t="s">
+        <v>257</v>
+      </c>
+      <c r="E720" t="s">
+        <v>63</v>
+      </c>
+      <c r="F720" t="s">
+        <v>13</v>
+      </c>
+      <c r="H720" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="721" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A721" t="s">
+        <v>254</v>
+      </c>
+      <c r="B721" t="s">
+        <v>255</v>
+      </c>
+      <c r="C721" t="s">
+        <v>258</v>
+      </c>
+      <c r="D721" t="s">
+        <v>259</v>
+      </c>
+      <c r="E721" t="s">
+        <v>63</v>
+      </c>
+      <c r="F721" t="s">
+        <v>13</v>
+      </c>
+      <c r="H721" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="722" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A722" t="s">
+        <v>254</v>
+      </c>
+      <c r="B722" t="s">
+        <v>255</v>
+      </c>
+      <c r="C722" t="s">
+        <v>260</v>
+      </c>
+      <c r="D722" t="s">
+        <v>261</v>
+      </c>
+      <c r="E722" t="s">
+        <v>63</v>
+      </c>
+      <c r="F722" t="s">
+        <v>13</v>
+      </c>
+      <c r="H722" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="723" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A723" t="s">
+        <v>254</v>
+      </c>
+      <c r="B723" t="s">
+        <v>255</v>
+      </c>
+      <c r="C723" t="s">
+        <v>262</v>
+      </c>
+      <c r="D723" t="s">
+        <v>263</v>
+      </c>
+      <c r="E723" t="s">
+        <v>63</v>
+      </c>
+      <c r="F723" t="s">
+        <v>13</v>
+      </c>
+      <c r="H723" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="724" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A724" t="s">
+        <v>254</v>
+      </c>
+      <c r="B724" t="s">
+        <v>255</v>
+      </c>
+      <c r="C724" t="s">
+        <v>264</v>
+      </c>
+      <c r="D724" t="s">
+        <v>265</v>
+      </c>
+      <c r="E724" t="s">
+        <v>63</v>
+      </c>
+      <c r="F724" t="s">
+        <v>13</v>
+      </c>
+      <c r="H724" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="725" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A725" t="s">
+        <v>254</v>
+      </c>
+      <c r="B725" t="s">
+        <v>255</v>
+      </c>
+      <c r="C725" t="s">
+        <v>266</v>
+      </c>
+      <c r="D725" t="s">
+        <v>267</v>
+      </c>
+      <c r="E725" t="s">
+        <v>63</v>
+      </c>
+      <c r="F725" t="s">
+        <v>13</v>
+      </c>
+      <c r="H725" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="726" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A726" t="s">
+        <v>254</v>
+      </c>
+      <c r="B726" t="s">
+        <v>255</v>
+      </c>
+      <c r="C726" t="s">
+        <v>268</v>
+      </c>
+      <c r="D726" t="s">
+        <v>269</v>
+      </c>
+      <c r="E726" t="s">
+        <v>63</v>
+      </c>
+      <c r="F726" t="s">
+        <v>13</v>
+      </c>
+      <c r="H726" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="727" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A727" t="s">
+        <v>254</v>
+      </c>
+      <c r="B727" t="s">
+        <v>255</v>
+      </c>
+      <c r="C727" t="s">
+        <v>270</v>
+      </c>
+      <c r="D727" t="s">
+        <v>271</v>
+      </c>
+      <c r="E727" t="s">
+        <v>63</v>
+      </c>
+      <c r="F727" t="s">
+        <v>13</v>
+      </c>
+      <c r="H727" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="728" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A728" t="s">
+        <v>254</v>
+      </c>
+      <c r="B728" t="s">
+        <v>255</v>
+      </c>
+      <c r="C728" t="s">
+        <v>272</v>
+      </c>
+      <c r="D728" t="s">
+        <v>273</v>
+      </c>
+      <c r="E728" t="s">
+        <v>63</v>
+      </c>
+      <c r="F728" t="s">
+        <v>13</v>
+      </c>
+      <c r="H728" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="729" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A729" t="s">
+        <v>254</v>
+      </c>
+      <c r="B729" t="s">
+        <v>255</v>
+      </c>
+      <c r="C729" t="s">
+        <v>274</v>
+      </c>
+      <c r="D729" t="s">
+        <v>275</v>
+      </c>
+      <c r="E729" t="s">
+        <v>63</v>
+      </c>
+      <c r="F729" t="s">
+        <v>13</v>
+      </c>
+      <c r="H729" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="730" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A730" t="s">
+        <v>254</v>
+      </c>
+      <c r="B730" t="s">
+        <v>255</v>
+      </c>
+      <c r="C730" t="s">
+        <v>276</v>
+      </c>
+      <c r="D730" t="s">
+        <v>277</v>
+      </c>
+      <c r="E730" t="s">
+        <v>63</v>
+      </c>
+      <c r="F730" t="s">
+        <v>13</v>
+      </c>
+      <c r="H730" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="731" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A731" t="s">
+        <v>254</v>
+      </c>
+      <c r="B731" t="s">
+        <v>255</v>
+      </c>
+      <c r="C731" t="s">
+        <v>278</v>
+      </c>
+      <c r="D731" t="s">
+        <v>279</v>
+      </c>
+      <c r="E731" t="s">
+        <v>63</v>
+      </c>
+      <c r="F731" t="s">
+        <v>13</v>
+      </c>
+      <c r="H731" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="732" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A732" t="s">
+        <v>254</v>
+      </c>
+      <c r="B732" t="s">
+        <v>255</v>
+      </c>
+      <c r="C732" t="s">
+        <v>280</v>
+      </c>
+      <c r="D732" t="s">
+        <v>281</v>
+      </c>
+      <c r="E732" t="s">
+        <v>63</v>
+      </c>
+      <c r="F732" t="s">
+        <v>13</v>
+      </c>
+      <c r="H732" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="733" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A733" t="s">
+        <v>256</v>
+      </c>
+      <c r="B733" t="s">
+        <v>257</v>
+      </c>
+      <c r="C733" t="s">
+        <v>258</v>
+      </c>
+      <c r="D733" t="s">
+        <v>259</v>
+      </c>
+      <c r="E733" t="s">
+        <v>63</v>
+      </c>
+      <c r="F733" t="s">
+        <v>13</v>
+      </c>
+      <c r="H733" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="734" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A734" t="s">
+        <v>256</v>
+      </c>
+      <c r="B734" t="s">
+        <v>257</v>
+      </c>
+      <c r="C734" t="s">
+        <v>260</v>
+      </c>
+      <c r="D734" t="s">
+        <v>261</v>
+      </c>
+      <c r="E734" t="s">
+        <v>63</v>
+      </c>
+      <c r="F734" t="s">
+        <v>13</v>
+      </c>
+      <c r="H734" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="735" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A735" t="s">
+        <v>256</v>
+      </c>
+      <c r="B735" t="s">
+        <v>257</v>
+      </c>
+      <c r="C735" t="s">
+        <v>262</v>
+      </c>
+      <c r="D735" t="s">
+        <v>263</v>
+      </c>
+      <c r="E735" t="s">
+        <v>63</v>
+      </c>
+      <c r="F735" t="s">
+        <v>13</v>
+      </c>
+      <c r="H735" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="736" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A736" t="s">
+        <v>256</v>
+      </c>
+      <c r="B736" t="s">
+        <v>257</v>
+      </c>
+      <c r="C736" t="s">
+        <v>264</v>
+      </c>
+      <c r="D736" t="s">
+        <v>265</v>
+      </c>
+      <c r="E736" t="s">
+        <v>63</v>
+      </c>
+      <c r="F736" t="s">
+        <v>13</v>
+      </c>
+      <c r="H736" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="737" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A737" t="s">
+        <v>256</v>
+      </c>
+      <c r="B737" t="s">
+        <v>257</v>
+      </c>
+      <c r="C737" t="s">
+        <v>266</v>
+      </c>
+      <c r="D737" t="s">
+        <v>267</v>
+      </c>
+      <c r="E737" t="s">
+        <v>63</v>
+      </c>
+      <c r="F737" t="s">
+        <v>13</v>
+      </c>
+      <c r="H737" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="738" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A738" t="s">
+        <v>256</v>
+      </c>
+      <c r="B738" t="s">
+        <v>257</v>
+      </c>
+      <c r="C738" t="s">
+        <v>268</v>
+      </c>
+      <c r="D738" t="s">
+        <v>269</v>
+      </c>
+      <c r="E738" t="s">
+        <v>63</v>
+      </c>
+      <c r="F738" t="s">
+        <v>13</v>
+      </c>
+      <c r="H738" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="739" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A739" t="s">
+        <v>256</v>
+      </c>
+      <c r="B739" t="s">
+        <v>257</v>
+      </c>
+      <c r="C739" t="s">
+        <v>270</v>
+      </c>
+      <c r="D739" t="s">
+        <v>271</v>
+      </c>
+      <c r="E739" t="s">
+        <v>63</v>
+      </c>
+      <c r="F739" t="s">
+        <v>13</v>
+      </c>
+      <c r="H739" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="740" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A740" t="s">
+        <v>256</v>
+      </c>
+      <c r="B740" t="s">
+        <v>257</v>
+      </c>
+      <c r="C740" t="s">
+        <v>272</v>
+      </c>
+      <c r="D740" t="s">
+        <v>273</v>
+      </c>
+      <c r="E740" t="s">
+        <v>63</v>
+      </c>
+      <c r="F740" t="s">
+        <v>13</v>
+      </c>
+      <c r="H740" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="741" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A741" t="s">
+        <v>256</v>
+      </c>
+      <c r="B741" t="s">
+        <v>257</v>
+      </c>
+      <c r="C741" t="s">
+        <v>274</v>
+      </c>
+      <c r="D741" t="s">
+        <v>275</v>
+      </c>
+      <c r="E741" t="s">
+        <v>63</v>
+      </c>
+      <c r="F741" t="s">
+        <v>13</v>
+      </c>
+      <c r="H741" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="742" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A742" t="s">
+        <v>256</v>
+      </c>
+      <c r="B742" t="s">
+        <v>257</v>
+      </c>
+      <c r="C742" t="s">
+        <v>276</v>
+      </c>
+      <c r="D742" t="s">
+        <v>277</v>
+      </c>
+      <c r="E742" t="s">
+        <v>63</v>
+      </c>
+      <c r="F742" t="s">
+        <v>13</v>
+      </c>
+      <c r="H742" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="743" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A743" t="s">
+        <v>256</v>
+      </c>
+      <c r="B743" t="s">
+        <v>257</v>
+      </c>
+      <c r="C743" t="s">
+        <v>278</v>
+      </c>
+      <c r="D743" t="s">
+        <v>279</v>
+      </c>
+      <c r="E743" t="s">
+        <v>63</v>
+      </c>
+      <c r="F743" t="s">
+        <v>13</v>
+      </c>
+      <c r="H743" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="744" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A744" t="s">
+        <v>256</v>
+      </c>
+      <c r="B744" t="s">
+        <v>257</v>
+      </c>
+      <c r="C744" t="s">
+        <v>280</v>
+      </c>
+      <c r="D744" t="s">
+        <v>281</v>
+      </c>
+      <c r="E744" t="s">
+        <v>63</v>
+      </c>
+      <c r="F744" t="s">
+        <v>13</v>
+      </c>
+      <c r="H744" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="745" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A745" t="s">
+        <v>258</v>
+      </c>
+      <c r="B745" t="s">
+        <v>259</v>
+      </c>
+      <c r="C745" t="s">
+        <v>260</v>
+      </c>
+      <c r="D745" t="s">
+        <v>261</v>
+      </c>
+      <c r="E745" t="s">
+        <v>48</v>
+      </c>
+      <c r="F745" t="s">
+        <v>13</v>
+      </c>
+      <c r="H745" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="746" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A746" t="s">
+        <v>258</v>
+      </c>
+      <c r="B746" t="s">
+        <v>259</v>
+      </c>
+      <c r="C746" t="s">
+        <v>262</v>
+      </c>
+      <c r="D746" t="s">
+        <v>263</v>
+      </c>
+      <c r="E746" t="s">
+        <v>48</v>
+      </c>
+      <c r="F746" t="s">
+        <v>13</v>
+      </c>
+      <c r="H746" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="747" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A747" t="s">
+        <v>258</v>
+      </c>
+      <c r="B747" t="s">
+        <v>259</v>
+      </c>
+      <c r="C747" t="s">
+        <v>264</v>
+      </c>
+      <c r="D747" t="s">
+        <v>265</v>
+      </c>
+      <c r="E747" t="s">
+        <v>48</v>
+      </c>
+      <c r="F747" t="s">
+        <v>13</v>
+      </c>
+      <c r="H747" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="748" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A748" t="s">
+        <v>258</v>
+      </c>
+      <c r="B748" t="s">
+        <v>259</v>
+      </c>
+      <c r="C748" t="s">
+        <v>266</v>
+      </c>
+      <c r="D748" t="s">
+        <v>267</v>
+      </c>
+      <c r="E748" t="s">
+        <v>48</v>
+      </c>
+      <c r="F748" t="s">
+        <v>13</v>
+      </c>
+      <c r="H748" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="749" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A749" t="s">
+        <v>258</v>
+      </c>
+      <c r="B749" t="s">
+        <v>259</v>
+      </c>
+      <c r="C749" t="s">
+        <v>268</v>
+      </c>
+      <c r="D749" t="s">
+        <v>269</v>
+      </c>
+      <c r="E749" t="s">
+        <v>48</v>
+      </c>
+      <c r="F749" t="s">
+        <v>13</v>
+      </c>
+      <c r="H749" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="750" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A750" t="s">
+        <v>258</v>
+      </c>
+      <c r="B750" t="s">
+        <v>259</v>
+      </c>
+      <c r="C750" t="s">
+        <v>270</v>
+      </c>
+      <c r="D750" t="s">
+        <v>271</v>
+      </c>
+      <c r="E750" t="s">
+        <v>48</v>
+      </c>
+      <c r="F750" t="s">
+        <v>13</v>
+      </c>
+      <c r="H750" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="751" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A751" t="s">
+        <v>258</v>
+      </c>
+      <c r="B751" t="s">
+        <v>259</v>
+      </c>
+      <c r="C751" t="s">
+        <v>272</v>
+      </c>
+      <c r="D751" t="s">
+        <v>273</v>
+      </c>
+      <c r="E751" t="s">
+        <v>48</v>
+      </c>
+      <c r="F751" t="s">
+        <v>13</v>
+      </c>
+      <c r="H751" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="752" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A752" t="s">
+        <v>258</v>
+      </c>
+      <c r="B752" t="s">
+        <v>259</v>
+      </c>
+      <c r="C752" t="s">
+        <v>274</v>
+      </c>
+      <c r="D752" t="s">
+        <v>275</v>
+      </c>
+      <c r="E752" t="s">
+        <v>48</v>
+      </c>
+      <c r="F752" t="s">
+        <v>13</v>
+      </c>
+      <c r="H752" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="753" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A753" t="s">
+        <v>258</v>
+      </c>
+      <c r="B753" t="s">
+        <v>259</v>
+      </c>
+      <c r="C753" t="s">
+        <v>276</v>
+      </c>
+      <c r="D753" t="s">
+        <v>277</v>
+      </c>
+      <c r="E753" t="s">
+        <v>48</v>
+      </c>
+      <c r="F753" t="s">
+        <v>13</v>
+      </c>
+      <c r="H753" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="754" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A754" t="s">
+        <v>258</v>
+      </c>
+      <c r="B754" t="s">
+        <v>259</v>
+      </c>
+      <c r="C754" t="s">
+        <v>278</v>
+      </c>
+      <c r="D754" t="s">
+        <v>279</v>
+      </c>
+      <c r="E754" t="s">
+        <v>48</v>
+      </c>
+      <c r="F754" t="s">
+        <v>13</v>
+      </c>
+      <c r="H754" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="755" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A755" t="s">
+        <v>258</v>
+      </c>
+      <c r="B755" t="s">
+        <v>259</v>
+      </c>
+      <c r="C755" t="s">
+        <v>280</v>
+      </c>
+      <c r="D755" t="s">
+        <v>281</v>
+      </c>
+      <c r="E755" t="s">
+        <v>48</v>
+      </c>
+      <c r="F755" t="s">
+        <v>13</v>
+      </c>
+      <c r="H755" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="756" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A756" t="s">
+        <v>260</v>
+      </c>
+      <c r="B756" t="s">
+        <v>261</v>
+      </c>
+      <c r="C756" t="s">
+        <v>262</v>
+      </c>
+      <c r="D756" t="s">
+        <v>263</v>
+      </c>
+      <c r="E756" t="s">
+        <v>48</v>
+      </c>
+      <c r="F756" t="s">
+        <v>13</v>
+      </c>
+      <c r="H756" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="757" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A757" t="s">
+        <v>260</v>
+      </c>
+      <c r="B757" t="s">
+        <v>261</v>
+      </c>
+      <c r="C757" t="s">
+        <v>264</v>
+      </c>
+      <c r="D757" t="s">
+        <v>265</v>
+      </c>
+      <c r="E757" t="s">
+        <v>48</v>
+      </c>
+      <c r="F757" t="s">
+        <v>13</v>
+      </c>
+      <c r="H757" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="758" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A758" t="s">
+        <v>260</v>
+      </c>
+      <c r="B758" t="s">
+        <v>261</v>
+      </c>
+      <c r="C758" t="s">
+        <v>266</v>
+      </c>
+      <c r="D758" t="s">
+        <v>267</v>
+      </c>
+      <c r="E758" t="s">
+        <v>48</v>
+      </c>
+      <c r="F758" t="s">
+        <v>13</v>
+      </c>
+      <c r="H758" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="759" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A759" t="s">
+        <v>260</v>
+      </c>
+      <c r="B759" t="s">
+        <v>261</v>
+      </c>
+      <c r="C759" t="s">
+        <v>268</v>
+      </c>
+      <c r="D759" t="s">
+        <v>269</v>
+      </c>
+      <c r="E759" t="s">
+        <v>48</v>
+      </c>
+      <c r="F759" t="s">
+        <v>13</v>
+      </c>
+      <c r="H759" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="760" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A760" t="s">
+        <v>260</v>
+      </c>
+      <c r="B760" t="s">
+        <v>261</v>
+      </c>
+      <c r="C760" t="s">
+        <v>270</v>
+      </c>
+      <c r="D760" t="s">
+        <v>271</v>
+      </c>
+      <c r="E760" t="s">
+        <v>48</v>
+      </c>
+      <c r="F760" t="s">
+        <v>13</v>
+      </c>
+      <c r="H760" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="761" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A761" t="s">
+        <v>260</v>
+      </c>
+      <c r="B761" t="s">
+        <v>261</v>
+      </c>
+      <c r="C761" t="s">
+        <v>272</v>
+      </c>
+      <c r="D761" t="s">
+        <v>273</v>
+      </c>
+      <c r="E761" t="s">
+        <v>48</v>
+      </c>
+      <c r="F761" t="s">
+        <v>13</v>
+      </c>
+      <c r="H761" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="762" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A762" t="s">
+        <v>260</v>
+      </c>
+      <c r="B762" t="s">
+        <v>261</v>
+      </c>
+      <c r="C762" t="s">
+        <v>274</v>
+      </c>
+      <c r="D762" t="s">
+        <v>275</v>
+      </c>
+      <c r="E762" t="s">
+        <v>48</v>
+      </c>
+      <c r="F762" t="s">
+        <v>13</v>
+      </c>
+      <c r="H762" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="763" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A763" t="s">
+        <v>260</v>
+      </c>
+      <c r="B763" t="s">
+        <v>261</v>
+      </c>
+      <c r="C763" t="s">
+        <v>276</v>
+      </c>
+      <c r="D763" t="s">
+        <v>277</v>
+      </c>
+      <c r="E763" t="s">
+        <v>48</v>
+      </c>
+      <c r="F763" t="s">
+        <v>13</v>
+      </c>
+      <c r="H763" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="764" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A764" t="s">
+        <v>260</v>
+      </c>
+      <c r="B764" t="s">
+        <v>261</v>
+      </c>
+      <c r="C764" t="s">
+        <v>278</v>
+      </c>
+      <c r="D764" t="s">
+        <v>279</v>
+      </c>
+      <c r="E764" t="s">
+        <v>48</v>
+      </c>
+      <c r="F764" t="s">
+        <v>13</v>
+      </c>
+      <c r="H764" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="765" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A765" t="s">
+        <v>260</v>
+      </c>
+      <c r="B765" t="s">
+        <v>261</v>
+      </c>
+      <c r="C765" t="s">
+        <v>280</v>
+      </c>
+      <c r="D765" t="s">
+        <v>281</v>
+      </c>
+      <c r="E765" t="s">
+        <v>48</v>
+      </c>
+      <c r="F765" t="s">
+        <v>13</v>
+      </c>
+      <c r="H765" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="766" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A766" t="s">
+        <v>262</v>
+      </c>
+      <c r="B766" t="s">
+        <v>263</v>
+      </c>
+      <c r="C766" t="s">
+        <v>264</v>
+      </c>
+      <c r="D766" t="s">
+        <v>265</v>
+      </c>
+      <c r="E766" t="s">
+        <v>48</v>
+      </c>
+      <c r="F766" t="s">
+        <v>13</v>
+      </c>
+      <c r="H766" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="767" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A767" t="s">
+        <v>262</v>
+      </c>
+      <c r="B767" t="s">
+        <v>263</v>
+      </c>
+      <c r="C767" t="s">
+        <v>266</v>
+      </c>
+      <c r="D767" t="s">
+        <v>267</v>
+      </c>
+      <c r="E767" t="s">
+        <v>48</v>
+      </c>
+      <c r="F767" t="s">
+        <v>13</v>
+      </c>
+      <c r="H767" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="768" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A768" t="s">
+        <v>262</v>
+      </c>
+      <c r="B768" t="s">
+        <v>263</v>
+      </c>
+      <c r="C768" t="s">
+        <v>268</v>
+      </c>
+      <c r="D768" t="s">
+        <v>269</v>
+      </c>
+      <c r="E768" t="s">
+        <v>48</v>
+      </c>
+      <c r="F768" t="s">
+        <v>13</v>
+      </c>
+      <c r="H768" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="769" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A769" t="s">
+        <v>262</v>
+      </c>
+      <c r="B769" t="s">
+        <v>263</v>
+      </c>
+      <c r="C769" t="s">
+        <v>270</v>
+      </c>
+      <c r="D769" t="s">
+        <v>271</v>
+      </c>
+      <c r="E769" t="s">
+        <v>48</v>
+      </c>
+      <c r="F769" t="s">
+        <v>13</v>
+      </c>
+      <c r="H769" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="770" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A770" t="s">
+        <v>262</v>
+      </c>
+      <c r="B770" t="s">
+        <v>263</v>
+      </c>
+      <c r="C770" t="s">
+        <v>272</v>
+      </c>
+      <c r="D770" t="s">
+        <v>273</v>
+      </c>
+      <c r="E770" t="s">
+        <v>48</v>
+      </c>
+      <c r="F770" t="s">
+        <v>13</v>
+      </c>
+      <c r="H770" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="771" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A771" t="s">
+        <v>262</v>
+      </c>
+      <c r="B771" t="s">
+        <v>263</v>
+      </c>
+      <c r="C771" t="s">
+        <v>274</v>
+      </c>
+      <c r="D771" t="s">
+        <v>275</v>
+      </c>
+      <c r="E771" t="s">
+        <v>48</v>
+      </c>
+      <c r="F771" t="s">
+        <v>13</v>
+      </c>
+      <c r="H771" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="772" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A772" t="s">
+        <v>262</v>
+      </c>
+      <c r="B772" t="s">
+        <v>263</v>
+      </c>
+      <c r="C772" t="s">
+        <v>276</v>
+      </c>
+      <c r="D772" t="s">
+        <v>277</v>
+      </c>
+      <c r="E772" t="s">
+        <v>48</v>
+      </c>
+      <c r="F772" t="s">
+        <v>13</v>
+      </c>
+      <c r="H772" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="773" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A773" t="s">
+        <v>262</v>
+      </c>
+      <c r="B773" t="s">
+        <v>263</v>
+      </c>
+      <c r="C773" t="s">
+        <v>278</v>
+      </c>
+      <c r="D773" t="s">
+        <v>279</v>
+      </c>
+      <c r="E773" t="s">
+        <v>48</v>
+      </c>
+      <c r="F773" t="s">
+        <v>13</v>
+      </c>
+      <c r="H773" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="774" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A774" t="s">
+        <v>262</v>
+      </c>
+      <c r="B774" t="s">
+        <v>263</v>
+      </c>
+      <c r="C774" t="s">
+        <v>280</v>
+      </c>
+      <c r="D774" t="s">
+        <v>281</v>
+      </c>
+      <c r="E774" t="s">
+        <v>48</v>
+      </c>
+      <c r="F774" t="s">
+        <v>13</v>
+      </c>
+      <c r="H774" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="775" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A775" t="s">
+        <v>264</v>
+      </c>
+      <c r="B775" t="s">
+        <v>265</v>
+      </c>
+      <c r="C775" t="s">
+        <v>266</v>
+      </c>
+      <c r="D775" t="s">
+        <v>267</v>
+      </c>
+      <c r="E775" t="s">
+        <v>63</v>
+      </c>
+      <c r="F775" t="s">
+        <v>13</v>
+      </c>
+      <c r="H775" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="776" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A776" t="s">
+        <v>264</v>
+      </c>
+      <c r="B776" t="s">
+        <v>265</v>
+      </c>
+      <c r="C776" t="s">
+        <v>268</v>
+      </c>
+      <c r="D776" t="s">
+        <v>269</v>
+      </c>
+      <c r="E776" t="s">
+        <v>63</v>
+      </c>
+      <c r="F776" t="s">
+        <v>13</v>
+      </c>
+      <c r="H776" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="777" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A777" t="s">
+        <v>264</v>
+      </c>
+      <c r="B777" t="s">
+        <v>265</v>
+      </c>
+      <c r="C777" t="s">
+        <v>270</v>
+      </c>
+      <c r="D777" t="s">
+        <v>271</v>
+      </c>
+      <c r="E777" t="s">
+        <v>63</v>
+      </c>
+      <c r="F777" t="s">
+        <v>13</v>
+      </c>
+      <c r="H777" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="778" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A778" t="s">
+        <v>264</v>
+      </c>
+      <c r="B778" t="s">
+        <v>265</v>
+      </c>
+      <c r="C778" t="s">
+        <v>272</v>
+      </c>
+      <c r="D778" t="s">
+        <v>273</v>
+      </c>
+      <c r="E778" t="s">
+        <v>63</v>
+      </c>
+      <c r="F778" t="s">
+        <v>13</v>
+      </c>
+      <c r="H778" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="779" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A779" t="s">
+        <v>264</v>
+      </c>
+      <c r="B779" t="s">
+        <v>265</v>
+      </c>
+      <c r="C779" t="s">
+        <v>274</v>
+      </c>
+      <c r="D779" t="s">
+        <v>275</v>
+      </c>
+      <c r="E779" t="s">
+        <v>63</v>
+      </c>
+      <c r="F779" t="s">
+        <v>13</v>
+      </c>
+      <c r="H779" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="780" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A780" t="s">
+        <v>264</v>
+      </c>
+      <c r="B780" t="s">
+        <v>265</v>
+      </c>
+      <c r="C780" t="s">
+        <v>276</v>
+      </c>
+      <c r="D780" t="s">
+        <v>277</v>
+      </c>
+      <c r="E780" t="s">
+        <v>63</v>
+      </c>
+      <c r="F780" t="s">
+        <v>13</v>
+      </c>
+      <c r="H780" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="781" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A781" t="s">
+        <v>264</v>
+      </c>
+      <c r="B781" t="s">
+        <v>265</v>
+      </c>
+      <c r="C781" t="s">
+        <v>278</v>
+      </c>
+      <c r="D781" t="s">
+        <v>279</v>
+      </c>
+      <c r="E781" t="s">
+        <v>63</v>
+      </c>
+      <c r="F781" t="s">
+        <v>13</v>
+      </c>
+      <c r="H781" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="782" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A782" t="s">
+        <v>264</v>
+      </c>
+      <c r="B782" t="s">
+        <v>265</v>
+      </c>
+      <c r="C782" t="s">
+        <v>280</v>
+      </c>
+      <c r="D782" t="s">
+        <v>281</v>
+      </c>
+      <c r="E782" t="s">
+        <v>63</v>
+      </c>
+      <c r="F782" t="s">
+        <v>13</v>
+      </c>
+      <c r="H782" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="783" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A783" t="s">
+        <v>266</v>
+      </c>
+      <c r="B783" t="s">
+        <v>267</v>
+      </c>
+      <c r="C783" t="s">
+        <v>268</v>
+      </c>
+      <c r="D783" t="s">
+        <v>269</v>
+      </c>
+      <c r="E783" t="s">
+        <v>63</v>
+      </c>
+      <c r="F783" t="s">
+        <v>13</v>
+      </c>
+      <c r="H783" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="784" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A784" t="s">
+        <v>266</v>
+      </c>
+      <c r="B784" t="s">
+        <v>267</v>
+      </c>
+      <c r="C784" t="s">
+        <v>270</v>
+      </c>
+      <c r="D784" t="s">
+        <v>271</v>
+      </c>
+      <c r="E784" t="s">
+        <v>63</v>
+      </c>
+      <c r="F784" t="s">
+        <v>13</v>
+      </c>
+      <c r="H784" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="785" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A785" t="s">
+        <v>266</v>
+      </c>
+      <c r="B785" t="s">
+        <v>267</v>
+      </c>
+      <c r="C785" t="s">
+        <v>272</v>
+      </c>
+      <c r="D785" t="s">
+        <v>273</v>
+      </c>
+      <c r="E785" t="s">
+        <v>63</v>
+      </c>
+      <c r="F785" t="s">
+        <v>13</v>
+      </c>
+      <c r="H785" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="786" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A786" t="s">
+        <v>266</v>
+      </c>
+      <c r="B786" t="s">
+        <v>267</v>
+      </c>
+      <c r="C786" t="s">
+        <v>274</v>
+      </c>
+      <c r="D786" t="s">
+        <v>275</v>
+      </c>
+      <c r="E786" t="s">
+        <v>63</v>
+      </c>
+      <c r="F786" t="s">
+        <v>13</v>
+      </c>
+      <c r="H786" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="787" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A787" t="s">
+        <v>266</v>
+      </c>
+      <c r="B787" t="s">
+        <v>267</v>
+      </c>
+      <c r="C787" t="s">
+        <v>276</v>
+      </c>
+      <c r="D787" t="s">
+        <v>277</v>
+      </c>
+      <c r="E787" t="s">
+        <v>63</v>
+      </c>
+      <c r="F787" t="s">
+        <v>13</v>
+      </c>
+      <c r="H787" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="788" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A788" t="s">
+        <v>266</v>
+      </c>
+      <c r="B788" t="s">
+        <v>267</v>
+      </c>
+      <c r="C788" t="s">
+        <v>278</v>
+      </c>
+      <c r="D788" t="s">
+        <v>279</v>
+      </c>
+      <c r="E788" t="s">
+        <v>63</v>
+      </c>
+      <c r="F788" t="s">
+        <v>13</v>
+      </c>
+      <c r="H788" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="789" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A789" t="s">
+        <v>266</v>
+      </c>
+      <c r="B789" t="s">
+        <v>267</v>
+      </c>
+      <c r="C789" t="s">
+        <v>280</v>
+      </c>
+      <c r="D789" t="s">
+        <v>281</v>
+      </c>
+      <c r="E789" t="s">
+        <v>63</v>
+      </c>
+      <c r="F789" t="s">
+        <v>13</v>
+      </c>
+      <c r="H789" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="790" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A790" t="s">
+        <v>268</v>
+      </c>
+      <c r="B790" t="s">
+        <v>269</v>
+      </c>
+      <c r="C790" t="s">
+        <v>270</v>
+      </c>
+      <c r="D790" t="s">
+        <v>271</v>
+      </c>
+      <c r="E790" t="s">
+        <v>48</v>
+      </c>
+      <c r="F790" t="s">
+        <v>13</v>
+      </c>
+      <c r="H790" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="791" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A791" t="s">
+        <v>268</v>
+      </c>
+      <c r="B791" t="s">
+        <v>269</v>
+      </c>
+      <c r="C791" t="s">
+        <v>272</v>
+      </c>
+      <c r="D791" t="s">
+        <v>273</v>
+      </c>
+      <c r="E791" t="s">
+        <v>48</v>
+      </c>
+      <c r="F791" t="s">
+        <v>13</v>
+      </c>
+      <c r="H791" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="792" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A792" t="s">
+        <v>268</v>
+      </c>
+      <c r="B792" t="s">
+        <v>269</v>
+      </c>
+      <c r="C792" t="s">
+        <v>274</v>
+      </c>
+      <c r="D792" t="s">
+        <v>275</v>
+      </c>
+      <c r="E792" t="s">
+        <v>48</v>
+      </c>
+      <c r="F792" t="s">
+        <v>13</v>
+      </c>
+      <c r="H792" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="793" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A793" t="s">
+        <v>268</v>
+      </c>
+      <c r="B793" t="s">
+        <v>269</v>
+      </c>
+      <c r="C793" t="s">
+        <v>276</v>
+      </c>
+      <c r="D793" t="s">
+        <v>277</v>
+      </c>
+      <c r="E793" t="s">
+        <v>48</v>
+      </c>
+      <c r="F793" t="s">
+        <v>13</v>
+      </c>
+      <c r="H793" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="794" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A794" t="s">
+        <v>268</v>
+      </c>
+      <c r="B794" t="s">
+        <v>269</v>
+      </c>
+      <c r="C794" t="s">
+        <v>278</v>
+      </c>
+      <c r="D794" t="s">
+        <v>279</v>
+      </c>
+      <c r="E794" t="s">
+        <v>48</v>
+      </c>
+      <c r="F794" t="s">
+        <v>13</v>
+      </c>
+      <c r="H794" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="795" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A795" t="s">
+        <v>268</v>
+      </c>
+      <c r="B795" t="s">
+        <v>269</v>
+      </c>
+      <c r="C795" t="s">
+        <v>280</v>
+      </c>
+      <c r="D795" t="s">
+        <v>281</v>
+      </c>
+      <c r="E795" t="s">
+        <v>48</v>
+      </c>
+      <c r="F795" t="s">
+        <v>13</v>
+      </c>
+      <c r="H795" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="796" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A796" t="s">
+        <v>270</v>
+      </c>
+      <c r="B796" t="s">
+        <v>271</v>
+      </c>
+      <c r="C796" t="s">
+        <v>272</v>
+      </c>
+      <c r="D796" t="s">
+        <v>273</v>
+      </c>
+      <c r="E796" t="s">
+        <v>48</v>
+      </c>
+      <c r="F796" t="s">
+        <v>13</v>
+      </c>
+      <c r="H796" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="797" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A797" t="s">
+        <v>270</v>
+      </c>
+      <c r="B797" t="s">
+        <v>271</v>
+      </c>
+      <c r="C797" t="s">
+        <v>274</v>
+      </c>
+      <c r="D797" t="s">
+        <v>275</v>
+      </c>
+      <c r="E797" t="s">
+        <v>48</v>
+      </c>
+      <c r="F797" t="s">
+        <v>13</v>
+      </c>
+      <c r="H797" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="798" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A798" t="s">
+        <v>270</v>
+      </c>
+      <c r="B798" t="s">
+        <v>271</v>
+      </c>
+      <c r="C798" t="s">
+        <v>276</v>
+      </c>
+      <c r="D798" t="s">
+        <v>277</v>
+      </c>
+      <c r="E798" t="s">
+        <v>48</v>
+      </c>
+      <c r="F798" t="s">
+        <v>13</v>
+      </c>
+      <c r="H798" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="799" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A799" t="s">
+        <v>270</v>
+      </c>
+      <c r="B799" t="s">
+        <v>271</v>
+      </c>
+      <c r="C799" t="s">
+        <v>278</v>
+      </c>
+      <c r="D799" t="s">
+        <v>279</v>
+      </c>
+      <c r="E799" t="s">
+        <v>48</v>
+      </c>
+      <c r="F799" t="s">
+        <v>13</v>
+      </c>
+      <c r="H799" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="800" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A800" t="s">
+        <v>270</v>
+      </c>
+      <c r="B800" t="s">
+        <v>271</v>
+      </c>
+      <c r="C800" t="s">
+        <v>280</v>
+      </c>
+      <c r="D800" t="s">
+        <v>281</v>
+      </c>
+      <c r="E800" t="s">
+        <v>48</v>
+      </c>
+      <c r="F800" t="s">
+        <v>13</v>
+      </c>
+      <c r="H800" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="801" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A801" t="s">
+        <v>272</v>
+      </c>
+      <c r="B801" t="s">
+        <v>273</v>
+      </c>
+      <c r="C801" t="s">
+        <v>274</v>
+      </c>
+      <c r="D801" t="s">
+        <v>275</v>
+      </c>
+      <c r="E801" t="s">
+        <v>63</v>
+      </c>
+      <c r="F801" t="s">
+        <v>13</v>
+      </c>
+      <c r="H801" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="802" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A802" t="s">
+        <v>272</v>
+      </c>
+      <c r="B802" t="s">
+        <v>273</v>
+      </c>
+      <c r="C802" t="s">
+        <v>276</v>
+      </c>
+      <c r="D802" t="s">
+        <v>277</v>
+      </c>
+      <c r="E802" t="s">
+        <v>63</v>
+      </c>
+      <c r="F802" t="s">
+        <v>13</v>
+      </c>
+      <c r="H802" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="803" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A803" t="s">
+        <v>272</v>
+      </c>
+      <c r="B803" t="s">
+        <v>273</v>
+      </c>
+      <c r="C803" t="s">
+        <v>278</v>
+      </c>
+      <c r="D803" t="s">
+        <v>279</v>
+      </c>
+      <c r="E803" t="s">
+        <v>63</v>
+      </c>
+      <c r="F803" t="s">
+        <v>13</v>
+      </c>
+      <c r="H803" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="804" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A804" t="s">
+        <v>272</v>
+      </c>
+      <c r="B804" t="s">
+        <v>273</v>
+      </c>
+      <c r="C804" t="s">
+        <v>280</v>
+      </c>
+      <c r="D804" t="s">
+        <v>281</v>
+      </c>
+      <c r="E804" t="s">
+        <v>63</v>
+      </c>
+      <c r="F804" t="s">
+        <v>13</v>
+      </c>
+      <c r="H804" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="805" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A805" t="s">
+        <v>274</v>
+      </c>
+      <c r="B805" t="s">
+        <v>275</v>
+      </c>
+      <c r="C805" t="s">
+        <v>276</v>
+      </c>
+      <c r="D805" t="s">
+        <v>277</v>
+      </c>
+      <c r="E805" t="s">
+        <v>48</v>
+      </c>
+      <c r="F805" t="s">
+        <v>13</v>
+      </c>
+      <c r="H805" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="806" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A806" t="s">
+        <v>274</v>
+      </c>
+      <c r="B806" t="s">
+        <v>275</v>
+      </c>
+      <c r="C806" t="s">
+        <v>278</v>
+      </c>
+      <c r="D806" t="s">
+        <v>279</v>
+      </c>
+      <c r="E806" t="s">
+        <v>48</v>
+      </c>
+      <c r="F806" t="s">
+        <v>13</v>
+      </c>
+      <c r="H806" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="807" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A807" t="s">
+        <v>274</v>
+      </c>
+      <c r="B807" t="s">
+        <v>275</v>
+      </c>
+      <c r="C807" t="s">
+        <v>280</v>
+      </c>
+      <c r="D807" t="s">
+        <v>281</v>
+      </c>
+      <c r="E807" t="s">
+        <v>48</v>
+      </c>
+      <c r="F807" t="s">
+        <v>13</v>
+      </c>
+      <c r="H807" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="808" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A808" t="s">
+        <v>276</v>
+      </c>
+      <c r="B808" t="s">
+        <v>277</v>
+      </c>
+      <c r="C808" t="s">
+        <v>278</v>
+      </c>
+      <c r="D808" t="s">
+        <v>279</v>
+      </c>
+      <c r="E808" t="s">
+        <v>48</v>
+      </c>
+      <c r="F808" t="s">
+        <v>13</v>
+      </c>
+      <c r="H808" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="809" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A809" t="s">
+        <v>276</v>
+      </c>
+      <c r="B809" t="s">
+        <v>277</v>
+      </c>
+      <c r="C809" t="s">
+        <v>280</v>
+      </c>
+      <c r="D809" t="s">
+        <v>281</v>
+      </c>
+      <c r="E809" t="s">
+        <v>48</v>
+      </c>
+      <c r="F809" t="s">
+        <v>13</v>
+      </c>
+      <c r="H809" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="810" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A810" t="s">
+        <v>278</v>
+      </c>
+      <c r="B810" t="s">
+        <v>279</v>
+      </c>
+      <c r="C810" t="s">
+        <v>280</v>
+      </c>
+      <c r="D810" t="s">
+        <v>281</v>
+      </c>
+      <c r="E810" t="s">
+        <v>63</v>
+      </c>
+      <c r="F810" t="s">
+        <v>13</v>
+      </c>
+      <c r="H810" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="821" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A821" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="B821" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="C821" t="s">
+        <v>8</v>
+      </c>
+      <c r="D821" t="s">
+        <v>9</v>
+      </c>
+      <c r="E821" t="s">
+        <v>337</v>
+      </c>
+      <c r="F821" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="822" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A822" t="s">
+        <v>335</v>
+      </c>
+      <c r="B822" t="s">
+        <v>336</v>
       </c>
     </row>
   </sheetData>

--- a/relationship_data_template.xlsx
+++ b/relationship_data_template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krish\OneDrive\Desktop\anime_ai\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krish\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4723F0A2-C930-42BD-99A3-5D9F2B83CEA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77F8AF4E-3941-4D7B-95C0-80C677F644FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1C80641A-8C68-4CCB-904C-C1A2FE90DEC2}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4974" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5092" uniqueCount="384">
   <si>
     <t>source_name</t>
   </si>
@@ -1038,23 +1038,158 @@
     <t>char_smoothie_charlotte</t>
   </si>
   <si>
-    <t>Konohagakure</t>
-  </si>
-  <si>
-    <t>org_konohagakure</t>
+    <t>org_straw_hat_pirates</t>
+  </si>
+  <si>
+    <t>Straw Hat Pirates</t>
+  </si>
+  <si>
+    <t>captain</t>
+  </si>
+  <si>
+    <t>organization</t>
+  </si>
+  <si>
+    <t>Zoro Roronoa</t>
+  </si>
+  <si>
+    <t>char_zoro_roronoa</t>
+  </si>
+  <si>
+    <t>Nami</t>
+  </si>
+  <si>
+    <t>char_nami</t>
+  </si>
+  <si>
+    <t>Franky</t>
+  </si>
+  <si>
+    <t>char_franky</t>
+  </si>
+  <si>
+    <t>Brook</t>
+  </si>
+  <si>
+    <t>char_brook</t>
+  </si>
+  <si>
+    <t>Chopper Tony Tony</t>
+  </si>
+  <si>
+    <t>char_chopper_tony_tony</t>
+  </si>
+  <si>
+    <t>vice_captain</t>
   </si>
   <si>
     <t>member</t>
   </si>
   <si>
-    <t>organization</t>
+    <t xml:space="preserve">Captain </t>
+  </si>
+  <si>
+    <t>Swordsman, 3 swords user</t>
+  </si>
+  <si>
+    <t>Navigator</t>
+  </si>
+  <si>
+    <t>Sniper</t>
+  </si>
+  <si>
+    <t>Cook</t>
+  </si>
+  <si>
+    <t>Shipwrighter</t>
+  </si>
+  <si>
+    <t>Doctor</t>
+  </si>
+  <si>
+    <t>Archeologist</t>
+  </si>
+  <si>
+    <t>Singer</t>
+  </si>
+  <si>
+    <t>char_jinbe</t>
+  </si>
+  <si>
+    <t>Jinbe</t>
+  </si>
+  <si>
+    <t>fishman</t>
+  </si>
+  <si>
+    <t>Survey Corps</t>
+  </si>
+  <si>
+    <t>org_survey_corps</t>
+  </si>
+  <si>
+    <t>Erwin Smith</t>
+  </si>
+  <si>
+    <t>char_erwin_smith</t>
+  </si>
+  <si>
+    <t>commander</t>
+  </si>
+  <si>
+    <t>Levi</t>
+  </si>
+  <si>
+    <t>char_levi</t>
+  </si>
+  <si>
+    <t>Captain of the Levi squad</t>
+  </si>
+  <si>
+    <t>Member of the levi squad</t>
+  </si>
+  <si>
+    <t>Mikasa Ackerman</t>
+  </si>
+  <si>
+    <t>char_mikasa_ackerman</t>
+  </si>
+  <si>
+    <t>Armin Arlert</t>
+  </si>
+  <si>
+    <t>char_armin_arlert</t>
+  </si>
+  <si>
+    <t>Hange Zoe</t>
+  </si>
+  <si>
+    <t>char_hange_zoe</t>
+  </si>
+  <si>
+    <t>Jean Kirstein</t>
+  </si>
+  <si>
+    <t>char_jean_kirstein</t>
+  </si>
+  <si>
+    <t>Connie Springer</t>
+  </si>
+  <si>
+    <t>char_connie_springer</t>
+  </si>
+  <si>
+    <t>Sasha Blouse</t>
+  </si>
+  <si>
+    <t>char_sasha_blouse</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1212,6 +1347,30 @@
       <sz val="7"/>
       <color rgb="FF12824D"/>
       <name val="Courier New"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFA2FCA2"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFCE9178"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFA2FCA2"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFA2FCA2"/>
+      <name val="Consolas"/>
       <family val="3"/>
     </font>
   </fonts>
@@ -1556,7 +1715,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1564,6 +1723,18 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1919,16 +2090,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1F906C6-76EC-4EFB-AFDE-921EF73AD1B4}">
-  <dimension ref="A1:H822"/>
+  <dimension ref="A1:H839"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="20.77734375" customWidth="1"/>
-    <col min="4" max="4" width="27.77734375" customWidth="1"/>
+    <col min="3" max="3" width="23.33203125" customWidth="1"/>
+    <col min="4" max="4" width="37.88671875" customWidth="1"/>
     <col min="5" max="5" width="17.88671875" customWidth="1"/>
     <col min="6" max="6" width="16.6640625" customWidth="1"/>
-    <col min="7" max="7" width="15" customWidth="1"/>
+    <col min="7" max="7" width="24.88671875" customWidth="1"/>
     <col min="8" max="8" width="19.33203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -18280,32 +18451,420 @@
         <v>63</v>
       </c>
     </row>
-    <row r="821" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="820" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A820" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="B820" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="C820" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D820" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="E820" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="F820" t="s">
+        <v>338</v>
+      </c>
+      <c r="G820" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="821" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A821" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="B821" t="s">
         <v>335</v>
       </c>
-      <c r="B821" s="4" t="s">
-        <v>336</v>
-      </c>
-      <c r="C821" t="s">
-        <v>8</v>
-      </c>
-      <c r="D821" t="s">
-        <v>9</v>
-      </c>
-      <c r="E821" t="s">
-        <v>337</v>
+      <c r="C821" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="D821" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="E821" s="6" t="s">
+        <v>349</v>
       </c>
       <c r="F821" t="s">
         <v>338</v>
       </c>
-    </row>
-    <row r="822" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G821" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="822" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A822" t="s">
+        <v>336</v>
+      </c>
+      <c r="B822" t="s">
         <v>335</v>
       </c>
-      <c r="B822" t="s">
+      <c r="C822" s="7" t="s">
+        <v>341</v>
+      </c>
+      <c r="D822" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="E822" t="s">
+        <v>350</v>
+      </c>
+      <c r="F822" t="s">
+        <v>338</v>
+      </c>
+      <c r="G822" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="823" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A823" t="s">
         <v>336</v>
+      </c>
+      <c r="B823" t="s">
+        <v>335</v>
+      </c>
+      <c r="C823" t="s">
+        <v>217</v>
+      </c>
+      <c r="D823" t="s">
+        <v>218</v>
+      </c>
+      <c r="E823" t="s">
+        <v>350</v>
+      </c>
+      <c r="F823" t="s">
+        <v>338</v>
+      </c>
+      <c r="G823" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="824" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A824" t="s">
+        <v>336</v>
+      </c>
+      <c r="B824" t="s">
+        <v>335</v>
+      </c>
+      <c r="C824" t="s">
+        <v>199</v>
+      </c>
+      <c r="D824" t="s">
+        <v>200</v>
+      </c>
+      <c r="E824" t="s">
+        <v>350</v>
+      </c>
+      <c r="F824" t="s">
+        <v>338</v>
+      </c>
+      <c r="G824" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="825" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A825" t="s">
+        <v>336</v>
+      </c>
+      <c r="B825" t="s">
+        <v>335</v>
+      </c>
+      <c r="C825" t="s">
+        <v>213</v>
+      </c>
+      <c r="D825" t="s">
+        <v>214</v>
+      </c>
+      <c r="E825" t="s">
+        <v>350</v>
+      </c>
+      <c r="F825" t="s">
+        <v>338</v>
+      </c>
+      <c r="G825" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="826" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A826" t="s">
+        <v>336</v>
+      </c>
+      <c r="B826" t="s">
+        <v>335</v>
+      </c>
+      <c r="C826" t="s">
+        <v>343</v>
+      </c>
+      <c r="D826" t="s">
+        <v>344</v>
+      </c>
+      <c r="E826" t="s">
+        <v>350</v>
+      </c>
+      <c r="F826" t="s">
+        <v>338</v>
+      </c>
+      <c r="G826" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="827" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A827" t="s">
+        <v>336</v>
+      </c>
+      <c r="B827" t="s">
+        <v>335</v>
+      </c>
+      <c r="C827" t="s">
+        <v>345</v>
+      </c>
+      <c r="D827" t="s">
+        <v>346</v>
+      </c>
+      <c r="E827" t="s">
+        <v>350</v>
+      </c>
+      <c r="F827" t="s">
+        <v>338</v>
+      </c>
+      <c r="G827" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="828" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A828" t="s">
+        <v>336</v>
+      </c>
+      <c r="B828" t="s">
+        <v>335</v>
+      </c>
+      <c r="C828" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="D828" s="7" t="s">
+        <v>348</v>
+      </c>
+      <c r="E828" t="s">
+        <v>350</v>
+      </c>
+      <c r="F828" t="s">
+        <v>338</v>
+      </c>
+      <c r="G828" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="829" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A829" t="s">
+        <v>336</v>
+      </c>
+      <c r="B829" t="s">
+        <v>335</v>
+      </c>
+      <c r="C829" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="D829" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="E829" t="s">
+        <v>350</v>
+      </c>
+      <c r="F829" t="s">
+        <v>338</v>
+      </c>
+      <c r="G829" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="831" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A831" t="s">
+        <v>363</v>
+      </c>
+      <c r="B831" t="s">
+        <v>364</v>
+      </c>
+      <c r="C831" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="D831" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="E831" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="F831" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="832" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A832" t="s">
+        <v>363</v>
+      </c>
+      <c r="B832" t="s">
+        <v>364</v>
+      </c>
+      <c r="C832" t="s">
+        <v>368</v>
+      </c>
+      <c r="D832" t="s">
+        <v>369</v>
+      </c>
+      <c r="E832" t="s">
+        <v>350</v>
+      </c>
+      <c r="F832" t="s">
+        <v>338</v>
+      </c>
+      <c r="G832" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="833" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A833" t="s">
+        <v>363</v>
+      </c>
+      <c r="B833" t="s">
+        <v>364</v>
+      </c>
+      <c r="C833" t="s">
+        <v>317</v>
+      </c>
+      <c r="D833" t="s">
+        <v>318</v>
+      </c>
+      <c r="E833" t="s">
+        <v>350</v>
+      </c>
+      <c r="F833" t="s">
+        <v>338</v>
+      </c>
+      <c r="G833" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="834" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A834" t="s">
+        <v>363</v>
+      </c>
+      <c r="B834" t="s">
+        <v>364</v>
+      </c>
+      <c r="C834" t="s">
+        <v>372</v>
+      </c>
+      <c r="D834" t="s">
+        <v>373</v>
+      </c>
+      <c r="E834" t="s">
+        <v>350</v>
+      </c>
+      <c r="F834" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="835" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A835" t="s">
+        <v>363</v>
+      </c>
+      <c r="B835" t="s">
+        <v>364</v>
+      </c>
+      <c r="C835" t="s">
+        <v>374</v>
+      </c>
+      <c r="D835" t="s">
+        <v>375</v>
+      </c>
+      <c r="E835" t="s">
+        <v>350</v>
+      </c>
+      <c r="F835" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="836" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A836" t="s">
+        <v>363</v>
+      </c>
+      <c r="B836" t="s">
+        <v>364</v>
+      </c>
+      <c r="C836" t="s">
+        <v>376</v>
+      </c>
+      <c r="D836" t="s">
+        <v>377</v>
+      </c>
+      <c r="E836" t="s">
+        <v>350</v>
+      </c>
+      <c r="F836" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="837" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A837" t="s">
+        <v>363</v>
+      </c>
+      <c r="B837" t="s">
+        <v>364</v>
+      </c>
+      <c r="C837" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="D837" t="s">
+        <v>379</v>
+      </c>
+      <c r="E837" t="s">
+        <v>350</v>
+      </c>
+      <c r="F837" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="838" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A838" t="s">
+        <v>363</v>
+      </c>
+      <c r="B838" t="s">
+        <v>364</v>
+      </c>
+      <c r="C838" t="s">
+        <v>380</v>
+      </c>
+      <c r="D838" t="s">
+        <v>381</v>
+      </c>
+      <c r="E838" t="s">
+        <v>350</v>
+      </c>
+      <c r="F838" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="839" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A839" t="s">
+        <v>363</v>
+      </c>
+      <c r="B839" t="s">
+        <v>364</v>
+      </c>
+      <c r="C839" t="s">
+        <v>382</v>
+      </c>
+      <c r="D839" t="s">
+        <v>383</v>
+      </c>
+      <c r="E839" t="s">
+        <v>350</v>
+      </c>
+      <c r="F839" t="s">
+        <v>338</v>
       </c>
     </row>
   </sheetData>
